--- a/Models/Яйца/results/Яйца - Результаты прогнозов ХВ.xlsx
+++ b/Models/Яйца/results/Яйца - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[50685.04, 48891.84, 53982.82]</t>
+          <t>[59945.34, 57559.29, 56489.42]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[46739.2, 48287.8, 64167.2]</t>
+          <t>[62899.9, 58300.1, 56071.5]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6315.487130501831</v>
+        <v>1775.09647885856</v>
       </c>
       <c r="G2" t="n">
-        <v>4911.418351327612</v>
+        <v>1371.098008969687</v>
       </c>
       <c r="H2" t="n">
-        <v>8.521594503774827</v>
+        <v>2.23775517450924</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[46756.38, 51642.25, 51453.59]</t>
+          <t>[59058.65, 57947.67, 54167.51]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[48287.8, 64167.2, 59663.6]</t>
+          <t>[58300.1, 56071.5, 52213.7]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8691.449547546154</v>
+        <v>1624.066750025822</v>
       </c>
       <c r="G3" t="n">
-        <v>7422.12625447326</v>
+        <v>1529.508715618264</v>
       </c>
       <c r="H3" t="n">
-        <v>12.15039359099027</v>
+        <v>2.796362014883966</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[52569.79, 52369.71, 58457.25]</t>
+          <t>[57548.43, 53798.82, 58236.09]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[64167.2, 59663.6, 60711.6]</t>
+          <t>[56071.5, 52213.7, 55640.3]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8016.290567885996</v>
+        <v>1952.097810852304</v>
       </c>
       <c r="G4" t="n">
-        <v>7048.547292434775</v>
+        <v>1885.946527502429</v>
       </c>
       <c r="H4" t="n">
-        <v>11.33731948173915</v>
+        <v>3.445049447017843</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[58329.06, 65051.12, 65612.23]</t>
+          <t>[53057.6, 57451.73, 53151.03]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[59663.6, 60711.6, 60767.6]</t>
+          <t>[52213.7, 55640.3, 54329.0]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3833.313919204127</v>
+        <v>1339.284160880499</v>
       </c>
       <c r="G5" t="n">
-        <v>3506.231558554396</v>
+        <v>1277.765056201756</v>
       </c>
       <c r="H5" t="n">
-        <v>5.785644264409571</v>
+        <v>2.346685743097932</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[65898.11, 66458.32, 65057.1]</t>
+          <t>[56953.5, 52698.63, 51168.69]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[60711.6, 60767.6, 64270.3]</t>
+          <t>[55640.3, 54329.0, 45131.6]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4468.528353410277</v>
+        <v>3689.130286578981</v>
       </c>
       <c r="G6" t="n">
-        <v>3888.009641154994</v>
+        <v>2993.551667603817</v>
       </c>
       <c r="H6" t="n">
-        <v>6.377265079505722</v>
+        <v>6.245902540798885</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[63567.86, 62260.51, 59592.76]</t>
+          <t>[52048.24, 50541.61, 56830.64]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[60767.6, 64270.3, 62899.9]</t>
+          <t>[54329.0, 45131.6, 60384.8]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2757.891117111964</v>
+        <v>3962.412012842256</v>
       </c>
       <c r="G7" t="n">
-        <v>2705.729815869223</v>
+        <v>3748.31017330845</v>
       </c>
       <c r="H7" t="n">
-        <v>4.331006105895471</v>
+        <v>7.357030922337514</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[60770.7, 58182.39, 55870.76]</t>
+          <t>[51722.25, 58142.63, 57480.5]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[64270.3, 62899.9, 58300.1]</t>
+          <t>[45131.6, 60384.8, 53061.5]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3669.866352522653</v>
+        <v>4760.657388690202</v>
       </c>
       <c r="G8" t="n">
-        <v>3548.814958659658</v>
+        <v>4417.274573991458</v>
       </c>
       <c r="H8" t="n">
-        <v>5.70403463671177</v>
+        <v>8.881465944765713</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[59945.34, 57559.29, 56489.42]</t>
+          <t>[54110.83, 53529.42, 59193.97]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[62899.9, 58300.1, 56071.5]</t>
+          <t>[60384.8, 53061.5, 62239.8]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1775.09647885856</v>
+        <v>4035.618526587551</v>
       </c>
       <c r="G9" t="n">
-        <v>1371.098008969687</v>
+        <v>3262.569297571749</v>
       </c>
       <c r="H9" t="n">
-        <v>2.23775517450924</v>
+        <v>5.388502545793393</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[59058.65, 57947.67, 54167.51]</t>
+          <t>[56667.44, 62632.97, 63145.57]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[58300.1, 56071.5, 52213.7]</t>
+          <t>[53061.5, 62239.8, 61806.4]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1624.066750025822</v>
+        <v>2232.394011213671</v>
       </c>
       <c r="G10" t="n">
-        <v>1529.508715618264</v>
+        <v>1779.427893249403</v>
       </c>
       <c r="H10" t="n">
-        <v>2.796362014883966</v>
+        <v>3.198066304596212</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[57548.43, 53798.82, 58236.09]</t>
+          <t>[60592.69, 61082.12, 60308.39]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[56071.5, 52213.7, 55640.3]</t>
+          <t>[62239.8, 61806.4, 62214.8]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1952.097810852304</v>
+        <v>1513.489676175845</v>
       </c>
       <c r="G11" t="n">
-        <v>1885.946527502429</v>
+        <v>1425.933955424912</v>
       </c>
       <c r="H11" t="n">
-        <v>3.445049447017843</v>
+        <v>2.294162658791506</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[17468.54, 14623.07, 17026.0]</t>
+          <t>[17530.06, 20392.92, 18917.93]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[17851.6, 14347.6, 15908.4]</t>
+          <t>[17751.9, 19636.9, 18993.4]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>700.392164795811</v>
+        <v>456.9729363184564</v>
       </c>
       <c r="G12" t="n">
-        <v>592.0422718100186</v>
+        <v>351.1099222052192</v>
       </c>
       <c r="H12" t="n">
-        <v>3.696992639490895</v>
+        <v>1.832337437472024</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[14731.68, 17151.88, 16481.42]</t>
+          <t>[20483.96, 19001.54, 17711.07]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[14347.6, 15908.4, 15198.5]</t>
+          <t>[19636.9, 18993.4, 19062.1]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1055.090457245115</v>
+        <v>920.6644512928951</v>
       </c>
       <c r="G13" t="n">
-        <v>970.1610249234018</v>
+        <v>735.4120752139801</v>
       </c>
       <c r="H13" t="n">
-        <v>6.311526620997062</v>
+        <v>3.814674121683771</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[16999.03, 16335.68, 18438.42]</t>
+          <t>[18727.19, 17458.43, 15915.33]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[15908.4, 15198.5, 16896.0]</t>
+          <t>[18993.4, 19062.1, 18775.5]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1273.017986540772</v>
+        <v>1899.404141593068</v>
       </c>
       <c r="G14" t="n">
-        <v>1256.744609282171</v>
+        <v>1576.684266425395</v>
       </c>
       <c r="H14" t="n">
-        <v>7.822266807142968</v>
+        <v>8.349333609647006</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[15968.39, 18023.96, 18481.31]</t>
+          <t>[17542.06, 15991.45, 17538.87]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[15198.5, 16896.0, 19630.8]</t>
+          <t>[19062.1, 18775.5, 20148.6]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1030.591599943662</v>
+        <v>2371.506912172934</v>
       </c>
       <c r="G15" t="n">
-        <v>1015.780559044953</v>
+        <v>2304.605893310629</v>
       </c>
       <c r="H15" t="n">
-        <v>5.865671281559295</v>
+        <v>11.91821653142041</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[17714.96, 18166.44, 18144.45]</t>
+          <t>[16451.55, 18035.68, 15036.07]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[16896.0, 19630.8, 20242.2]</t>
+          <t>[18775.5, 20148.6, 17195.1]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1550.869979503089</v>
+        <v>2200.498602110989</v>
       </c>
       <c r="G16" t="n">
-        <v>1460.356749067299</v>
+        <v>2198.633243413922</v>
       </c>
       <c r="H16" t="n">
-        <v>7.556607380418267</v>
+        <v>11.80677461213923</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[17860.78, 17841.94, 16433.34]</t>
+          <t>[18923.19, 15765.8, 18255.32]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[19630.8, 20242.2, 17751.9]</t>
+          <t>[20148.6, 17195.1, 19281.6]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1882.623754485816</v>
+        <v>1237.980351113137</v>
       </c>
       <c r="G17" t="n">
-        <v>1829.613287347516</v>
+        <v>1226.997605566158</v>
       </c>
       <c r="H17" t="n">
-        <v>9.433986820968887</v>
+        <v>6.572238597656799</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[18439.8, 16981.6, 19760.84]</t>
+          <t>[16170.4, 18719.86, 17961.14]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[20242.2, 17751.9, 19636.9]</t>
+          <t>[17195.1, 19281.6, 19471.9]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1133.927558313921</v>
+        <v>1102.718590136018</v>
       </c>
       <c r="G18" t="n">
-        <v>898.8815009500892</v>
+        <v>1032.401537557301</v>
       </c>
       <c r="H18" t="n">
-        <v>4.62486820396433</v>
+        <v>5.543765418094443</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[17530.06, 20392.92, 18917.93]</t>
+          <t>[19197.91, 18417.9, 20732.64]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[17751.9, 19636.9, 18993.4]</t>
+          <t>[19281.6, 19471.9, 19921.5]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>456.9729363184564</v>
+        <v>769.3843144167903</v>
       </c>
       <c r="G19" t="n">
-        <v>351.1099222052192</v>
+        <v>649.6067095155207</v>
       </c>
       <c r="H19" t="n">
-        <v>1.832337437472024</v>
+        <v>3.306199912662262</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[20483.96, 19001.54, 17711.07]</t>
+          <t>[18449.62, 20764.19, 21531.2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[19636.9, 18993.4, 19062.1]</t>
+          <t>[19471.9, 19921.5, 19866.6]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>920.6644512928951</v>
+        <v>1228.289131245728</v>
       </c>
       <c r="G20" t="n">
-        <v>735.4120752139801</v>
+        <v>1176.523655876885</v>
       </c>
       <c r="H20" t="n">
-        <v>3.814674121683771</v>
+        <v>5.952990762906833</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[18727.19, 17458.43, 15915.33]</t>
+          <t>[21224.29, 22001.17, 22008.95]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[18993.4, 19062.1, 18775.5]</t>
+          <t>[19921.5, 19866.6, 21013.7]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1899.404141593068</v>
+        <v>1553.937673480089</v>
       </c>
       <c r="G21" t="n">
-        <v>1576.684266425395</v>
+        <v>1477.536146310347</v>
       </c>
       <c r="H21" t="n">
-        <v>8.349333609647006</v>
+        <v>7.340107246621465</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[40727.05, 38604.67, 45322.12]</t>
+          <t>[40619.69, 41824.52, 42480.61]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[43730.7, 40363.1, 45004.5]</t>
+          <t>[43050.1, 46554.1, 49803.9]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2017.828411238612</v>
+        <v>5225.142795737504</v>
       </c>
       <c r="G22" t="n">
-        <v>1693.233628944746</v>
+        <v>4827.759015921091</v>
       </c>
       <c r="H22" t="n">
-        <v>3.976932900186446</v>
+        <v>10.16970091783076</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[41143.26, 48270.65, 47885.84]</t>
+          <t>[44039.08, 44710.29, 41006.21]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[40363.1, 45004.5, 41819.3]</t>
+          <t>[46554.1, 49803.9, 51729.5]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4003.301158927356</v>
+        <v>7006.165476061688</v>
       </c>
       <c r="G23" t="n">
-        <v>3370.950002111912</v>
+        <v>6110.639751802167</v>
       </c>
       <c r="H23" t="n">
-        <v>7.898932123537278</v>
+        <v>12.11974527100813</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[47453.49, 47083.01, 49491.74]</t>
+          <t>[46977.04, 43068.34, 46254.81]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[45004.5, 41819.3, 42903.3]</t>
+          <t>[49803.9, 51729.5, 47398.6]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5069.90217535049</v>
+        <v>5301.415699372045</v>
       </c>
       <c r="G24" t="n">
-        <v>4767.046185284482</v>
+        <v>4210.600655096336</v>
       </c>
       <c r="H24" t="n">
-        <v>11.12831217923579</v>
+        <v>8.277422993124565</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[44906.04, 47223.2, 46179.76]</t>
+          <t>[45383.84, 48719.39, 43026.74]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[41819.3, 42903.3, 44604.4]</t>
+          <t>[51729.5, 47398.6, 41510.5]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3197.460605023469</v>
+        <v>3843.210768874432</v>
       </c>
       <c r="G25" t="n">
-        <v>2994.000263881712</v>
+        <v>3060.893445119936</v>
       </c>
       <c r="H25" t="n">
-        <v>6.993970028365604</v>
+        <v>6.235403083431384</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[44294.64, 43342.5, 40640.97]</t>
+          <t>[54874.08, 48405.93, 45697.62]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[42903.3, 44604.4, 38668.6]</t>
+          <t>[47398.6, 41510.5, 38920.1]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1572.520863750944</v>
+        <v>7056.075860008494</v>
       </c>
       <c r="G26" t="n">
-        <v>1541.870331696145</v>
+        <v>7049.478634769599</v>
       </c>
       <c r="H26" t="n">
-        <v>3.724254889947417</v>
+        <v>16.59891917915749</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[42111.55, 39497.23, 41188.42]</t>
+          <t>[42545.89, 40209.07, 46943.67]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[44604.4, 38668.6, 43050.1]</t>
+          <t>[41510.5, 38920.1, 41024.7]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1858.919894433463</v>
+        <v>3548.131219193669</v>
       </c>
       <c r="G27" t="n">
-        <v>1727.717421148533</v>
+        <v>2747.779223997738</v>
       </c>
       <c r="H27" t="n">
-        <v>4.018710597459338</v>
+        <v>6.744653478344585</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[41593.26, 43353.0, 44612.93]</t>
+          <t>[39338.57, 45934.02, 45287.07]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[38668.6, 43050.1, 46554.1]</t>
+          <t>[38920.1, 41024.7, 40330.8]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2034.168655010977</v>
+        <v>4034.896008132535</v>
       </c>
       <c r="G28" t="n">
-        <v>1722.90934851046</v>
+        <v>3428.021664355503</v>
       </c>
       <c r="H28" t="n">
-        <v>4.145566569038393</v>
+        <v>8.44366733399503</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[40619.69, 41824.52, 42480.61]</t>
+          <t>[45503.38, 44864.39, 47060.76]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[43050.1, 46554.1, 49803.9]</t>
+          <t>[41024.7, 40330.8, 42775.5]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5225.142795737504</v>
+        <v>4433.789127217661</v>
       </c>
       <c r="G29" t="n">
-        <v>4827.759015921091</v>
+        <v>4432.509703637581</v>
       </c>
       <c r="H29" t="n">
-        <v>10.16970091783076</v>
+        <v>10.72535561405429</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[44039.08, 44710.29, 41006.21]</t>
+          <t>[40920.6, 42954.87, 42294.04]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[46554.1, 49803.9, 51729.5]</t>
+          <t>[40330.8, 42775.5, 38080.1]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7006.165476061688</v>
+        <v>2458.813179509146</v>
       </c>
       <c r="G30" t="n">
-        <v>6110.639751802167</v>
+        <v>1661.035237000164</v>
       </c>
       <c r="H30" t="n">
-        <v>12.11974527100813</v>
+        <v>4.315904310117593</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[46977.04, 43068.34, 46254.81]</t>
+          <t>[42401.86, 41753.83, 38856.97]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[49803.9, 51729.5, 47398.6]</t>
+          <t>[42775.5, 38080.1, 34238.1]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5301.415699372045</v>
+        <v>3414.17904629012</v>
       </c>
       <c r="G31" t="n">
-        <v>4210.600655096336</v>
+        <v>2888.746989830916</v>
       </c>
       <c r="H31" t="n">
-        <v>8.277422993124565</v>
+        <v>8.003769045823539</v>
       </c>
     </row>
     <row r="32">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[1687.12, 1732.96, 1886.26]</t>
+          <t>[2251.96, 2147.38, 2025.69]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[1750.4, 1637.7, 1784.4]</t>
+          <t>[3327.4, 3278.0, 3283.5]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>88.41958059205128</v>
+        <v>1157.146385142899</v>
       </c>
       <c r="G32" t="n">
-        <v>86.79979590102471</v>
+        <v>1154.623990295688</v>
       </c>
       <c r="H32" t="n">
-        <v>5.046735777135699</v>
+        <v>35.03964453691808</v>
       </c>
     </row>
     <row r="33">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[1797.3, 1955.6, 1950.15]</t>
+          <t>[3161.86, 2972.37, 3377.93]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[1637.7, 1784.4, 1712.4]</t>
+          <t>[3278.0, 3283.5, 3123.7]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>192.6202810049521</v>
+        <v>241.4679341596955</v>
       </c>
       <c r="G33" t="n">
-        <v>189.5175789303644</v>
+        <v>227.1649333075525</v>
       </c>
       <c r="H33" t="n">
-        <v>11.07460945443581</v>
+        <v>7.052385800549373</v>
       </c>
     </row>
     <row r="34">
@@ -1630,32 +1630,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[1783.36, 1779.8, 1723.35]</t>
+          <t>[3080.6, 3499.83, 4065.28]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[1784.4, 1712.4, 1822.6]</t>
+          <t>[3283.5, 3123.7, 3581.1]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>69.26792750297152</v>
+        <v>372.8619277653081</v>
       </c>
       <c r="G34" t="n">
-        <v>55.89567708564353</v>
+        <v>354.4051576340482</v>
       </c>
       <c r="H34" t="n">
-        <v>3.146543670359891</v>
+        <v>10.58038068405057</v>
       </c>
     </row>
     <row r="35">
@@ -1666,32 +1666,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[1780.81, 1724.29, 1405.23]</t>
+          <t>[3728.21, 4328.17, 4340.4]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[1712.4, 1822.6, 1773.7]</t>
+          <t>[3123.7, 3581.1, 4789.5]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>223.6947955976173</v>
+        <v>612.4356777846674</v>
       </c>
       <c r="G35" t="n">
-        <v>178.3985815960458</v>
+        <v>600.2257903929194</v>
       </c>
       <c r="H35" t="n">
-        <v>10.05444625010058</v>
+        <v>16.53016618208868</v>
       </c>
     </row>
     <row r="36">
@@ -1702,32 +1702,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[1658.62, 1352.17, 1305.74]</t>
+          <t>[3632.15, 3648.52, 3688.93]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[1822.6, 1773.7, 2353.9]</t>
+          <t>[3581.1, 4789.5, 4333.4]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>659.0910471879156</v>
+        <v>757.140776546392</v>
       </c>
       <c r="G36" t="n">
-        <v>544.5532390381579</v>
+        <v>612.1673648324673</v>
       </c>
       <c r="H36" t="n">
-        <v>25.7635840312417</v>
+        <v>13.37342291820358</v>
       </c>
     </row>
     <row r="37">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[1484.64, 1432.48, 1376.4]</t>
+          <t>[3597.73, 3637.99, 3935.12]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[1773.7, 2353.9, 3327.4]</t>
+          <t>[4789.5, 4333.4, 4701.3]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1256.843953929303</v>
+        <v>911.2161489486595</v>
       </c>
       <c r="G37" t="n">
-        <v>1053.827827517349</v>
+        <v>884.4543602109521</v>
       </c>
       <c r="H37" t="n">
-        <v>38.02532704119193</v>
+        <v>19.07597220395578</v>
       </c>
     </row>
     <row r="38">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[1708.75, 1639.36, 1567.6]</t>
+          <t>[4831.6, 5213.81, 5136.09]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[2353.9, 3327.4, 3278.0]</t>
+          <t>[4333.4, 4701.3, 4444.1]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1436.56517723528</v>
+        <v>574.3746930924675</v>
       </c>
       <c r="G38" t="n">
-        <v>1347.86213917797</v>
+        <v>567.5663721688885</v>
       </c>
       <c r="H38" t="n">
-        <v>43.43907571550634</v>
+        <v>12.65638486449003</v>
       </c>
     </row>
     <row r="39">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[2251.96, 2147.38, 2025.69]</t>
+          <t>[4680.07, 4614.11, 4473.07]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[3327.4, 3278.0, 3283.5]</t>
+          <t>[4701.3, 4444.1, 4447.7]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1157.146385142899</v>
+        <v>99.99559051828304</v>
       </c>
       <c r="G39" t="n">
-        <v>1154.623990295688</v>
+        <v>72.20364280001529</v>
       </c>
       <c r="H39" t="n">
-        <v>35.03964453691808</v>
+        <v>1.615841453623372</v>
       </c>
     </row>
     <row r="40">
@@ -1846,32 +1846,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[3161.86, 2972.37, 3377.93]</t>
+          <t>[4634.93, 4493.12, 3696.76]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[3278.0, 3283.5, 3123.7]</t>
+          <t>[4444.1, 4447.7, 4083.3]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>241.4679341596955</v>
+        <v>250.2582378338307</v>
       </c>
       <c r="G40" t="n">
-        <v>227.1649333075525</v>
+        <v>207.5946713099949</v>
       </c>
       <c r="H40" t="n">
-        <v>7.052385800549373</v>
+        <v>4.927142998760817</v>
       </c>
     </row>
     <row r="41">
@@ -1882,32 +1882,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[3080.6, 3499.83, 4065.28]</t>
+          <t>[4309.61, 3546.94, 3506.71]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[3283.5, 3123.7, 3581.1]</t>
+          <t>[4447.7, 4083.3, 3883.1]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>372.8619277653081</v>
+        <v>386.6191130167182</v>
       </c>
       <c r="G41" t="n">
-        <v>354.4051576340482</v>
+        <v>350.2810200036235</v>
       </c>
       <c r="H41" t="n">
-        <v>10.58038068405057</v>
+        <v>8.644432886667147</v>
       </c>
     </row>
     <row r="42">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[3076.76, 3426.27, 5258.92]</t>
+          <t>[5772.97, 5531.88, 4493.81]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[2905.2, 3066.1, 4495.1]</t>
+          <t>[5916.0, 5600.6, 4681.3]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>497.5161785261081</v>
+        <v>141.812179235464</v>
       </c>
       <c r="G42" t="n">
-        <v>431.8467556712761</v>
+        <v>133.0804056997082</v>
       </c>
       <c r="H42" t="n">
-        <v>11.54804046278432</v>
+        <v>2.549927909919104</v>
       </c>
     </row>
     <row r="43">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[3263.49, 5011.25, 5558.23]</t>
+          <t>[5647.1, 4586.66, 4129.16]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[3066.1, 4495.1, 5347.9]</t>
+          <t>[5600.6, 4681.3, 4394.2]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>341.3767528490509</v>
+        <v>164.6890855277396</v>
       </c>
       <c r="G43" t="n">
-        <v>307.9558313614925</v>
+        <v>135.394781034709</v>
       </c>
       <c r="H43" t="n">
-        <v>7.284398239411634</v>
+        <v>2.961205923196689</v>
       </c>
     </row>
     <row r="44">
@@ -1990,32 +1990,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[4751.94, 5273.07, 7171.15]</t>
+          <t>[4554.89, 4100.82, 4197.43]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[4495.1, 5347.9, 6670.2]</t>
+          <t>[4681.3, 4394.2, 4553.1]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>327.8778900817084</v>
+        <v>276.013019494355</v>
       </c>
       <c r="G44" t="n">
-        <v>277.5373885742413</v>
+        <v>258.4848815867105</v>
       </c>
       <c r="H44" t="n">
-        <v>4.874379908910307</v>
+        <v>5.729442979638172</v>
       </c>
     </row>
     <row r="45">
@@ -2026,32 +2026,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[5028.17, 6840.52, 7325.02]</t>
+          <t>[4196.16, 4294.14, 2699.54]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[5347.9, 6670.2, 7405.6]</t>
+          <t>[4394.2, 4553.1, 2154.3]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>214.2668927646112</v>
+        <v>366.7728287144562</v>
       </c>
       <c r="G45" t="n">
-        <v>190.2102007479883</v>
+        <v>334.0798381714782</v>
       </c>
       <c r="H45" t="n">
-        <v>3.206725420990066</v>
+        <v>11.8345949070124</v>
       </c>
     </row>
     <row r="46">
@@ -2062,32 +2062,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[7209.56, 7716.44, 6611.88]</t>
+          <t>[4464.05, 2805.42, 3109.78]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[6670.2, 7405.6, 6088.3]</t>
+          <t>[4553.1, 2154.3, 2920.8]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>469.6346440371302</v>
+        <v>394.8001355413725</v>
       </c>
       <c r="G46" t="n">
-        <v>457.9272303601771</v>
+        <v>309.7167657620295</v>
       </c>
       <c r="H46" t="n">
-        <v>6.961096021600512</v>
+        <v>12.88338640263287</v>
       </c>
     </row>
     <row r="47">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[7225.95, 6195.09, 5839.96]</t>
+          <t>[2852.58, 3161.62, 4833.51]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[7405.6, 6088.3, 5916.0]</t>
+          <t>[2154.3, 2920.8, 3721.0]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>128.3998928129862</v>
+        <v>770.9890284541942</v>
       </c>
       <c r="G47" t="n">
-        <v>120.8261132370529</v>
+        <v>683.8693021001795</v>
       </c>
       <c r="H47" t="n">
-        <v>1.821731488057101</v>
+        <v>23.51878212950837</v>
       </c>
     </row>
     <row r="48">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[6324.84, 5961.18, 5710.71]</t>
+          <t>[2502.62, 3833.98, 4292.3]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[6088.3, 5916.0, 5600.6]</t>
+          <t>[2920.8, 3721.0, 4525.3]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>152.8791977133258</v>
+        <v>283.9762286181459</v>
       </c>
       <c r="G48" t="n">
-        <v>130.6096147408619</v>
+        <v>254.7188893032639</v>
       </c>
       <c r="H48" t="n">
-        <v>2.204954692229246</v>
+        <v>7.500778671501311</v>
       </c>
     </row>
     <row r="49">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[5772.97, 5531.88, 4493.81]</t>
+          <t>[4337.52, 4851.45, 6546.3]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[5916.0, 5600.6, 4681.3]</t>
+          <t>[3721.0, 4525.3, 6128.1]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>141.812179235464</v>
+        <v>469.5271905709859</v>
       </c>
       <c r="G49" t="n">
-        <v>133.0804056997082</v>
+        <v>453.6249029346179</v>
       </c>
       <c r="H49" t="n">
-        <v>2.549927909919104</v>
+        <v>10.20011587924647</v>
       </c>
     </row>
     <row r="50">
@@ -2206,32 +2206,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[5647.1, 4586.66, 4129.16]</t>
+          <t>[4313.43, 5825.88, 6269.91]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[5600.6, 4681.3, 4394.2]</t>
+          <t>[4525.3, 6128.1, 6290.9]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>164.6890855277396</v>
+        <v>213.4385919583233</v>
       </c>
       <c r="G50" t="n">
-        <v>135.394781034709</v>
+        <v>178.3613044091853</v>
       </c>
       <c r="H50" t="n">
-        <v>2.961205923196689</v>
+        <v>3.315784909801744</v>
       </c>
     </row>
     <row r="51">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[4554.89, 4100.82, 4197.43]</t>
+          <t>[6042.74, 6501.43, 5556.35]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[4681.3, 4394.2, 4553.1]</t>
+          <t>[6128.1, 6290.9, 6076.4]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>276.013019494355</v>
+        <v>327.6488582085837</v>
       </c>
       <c r="G51" t="n">
-        <v>258.4848815867105</v>
+        <v>271.9805819333096</v>
       </c>
       <c r="H51" t="n">
-        <v>5.729442979638172</v>
+        <v>4.432685643974051</v>
       </c>
     </row>
     <row r="52">
@@ -2278,32 +2278,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[33.01, 18.41, 15.88]</t>
+          <t>[15.95, 15.75, 18.28]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[17.2, 16.9, 16.6]</t>
+          <t>[15.7, 15.5, 15.1]</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>9.181875192253143</v>
+        <v>1.844675381234297</v>
       </c>
       <c r="G52" t="n">
-        <v>6.016717330655474</v>
+        <v>1.224087515936692</v>
       </c>
       <c r="H52" t="n">
-        <v>35.0835326007686</v>
+        <v>8.071363886885157</v>
       </c>
     </row>
     <row r="53">
@@ -2314,32 +2314,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[17.26, 14.59, 17.31]</t>
+          <t>[15.73, 18.27, 18.77]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[16.9, 16.6, 16.2]</t>
+          <t>[15.5, 15.1, 15.0]</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.338051666760148</v>
+        <v>2.843886878136894</v>
       </c>
       <c r="G53" t="n">
-        <v>1.155979391829132</v>
+        <v>2.386112113619367</v>
       </c>
       <c r="H53" t="n">
-        <v>7.005846027275357</v>
+        <v>15.84465029023624</v>
       </c>
     </row>
     <row r="54">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[14.57, 17.28, 15.47]</t>
+          <t>[18.26, 18.76, 16.64]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[16.6, 16.2, 16.1]</t>
+          <t>[15.1, 15.0, 15.1]</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.375619744899555</v>
+        <v>2.971452776411701</v>
       </c>
       <c r="G54" t="n">
-        <v>1.244523895599751</v>
+        <v>2.81974625567763</v>
       </c>
       <c r="H54" t="n">
-        <v>7.589518355083275</v>
+        <v>18.7291501732771</v>
       </c>
     </row>
     <row r="55">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[17.44, 15.61, 30.41]</t>
+          <t>[18.5, 16.51, 17.84]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[16.2, 16.1, 15.8]</t>
+          <t>[15.0, 15.1, 14.9]</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>8.469707406748611</v>
+        <v>2.762374024402538</v>
       </c>
       <c r="G55" t="n">
-        <v>5.448315615846578</v>
+        <v>2.618222578707444</v>
       </c>
       <c r="H55" t="n">
-        <v>34.39886866616263</v>
+        <v>17.47789649552758</v>
       </c>
     </row>
     <row r="56">
@@ -2422,32 +2422,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[15.53, 30.28, 15.66]</t>
+          <t>[16.38, 17.59, 16.43]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[16.1, 15.8, 15.8]</t>
+          <t>[15.1, 14.9, 14.9]</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>8.367877531930343</v>
+        <v>1.93291386114504</v>
       </c>
       <c r="G56" t="n">
-        <v>5.065689405205464</v>
+        <v>1.834068938426946</v>
       </c>
       <c r="H56" t="n">
-        <v>32.0388652144952</v>
+        <v>12.27111304398118</v>
       </c>
     </row>
     <row r="57">
@@ -2458,32 +2458,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[30.28, 15.7, 15.46]</t>
+          <t>[17.53, 16.37, 15.52]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[15.8, 15.8, 15.7]</t>
+          <t>[14.9, 14.9, 14.7]</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>8.362062777999085</v>
+        <v>1.802602469255105</v>
       </c>
       <c r="G57" t="n">
-        <v>4.94008652587878</v>
+        <v>1.64048795582719</v>
       </c>
       <c r="H57" t="n">
-        <v>31.26952833524824</v>
+        <v>11.03509395982298</v>
       </c>
     </row>
     <row r="58">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[16.24, 15.98, 15.78]</t>
+          <t>[16.26, 15.44, 15.62]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[15.8, 15.7, 15.5]</t>
+          <t>[14.9, 14.7, 14.5]</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.3407919605966886</v>
+        <v>1.099854289860107</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3328631748070343</v>
+        <v>1.069895633154325</v>
       </c>
       <c r="H58" t="n">
-        <v>2.121907416832862</v>
+        <v>7.271786316709983</v>
       </c>
     </row>
     <row r="59">
@@ -2530,32 +2530,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[15.95, 15.75, 18.28]</t>
+          <t>[15.37, 15.55, 15.32]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[15.7, 15.5, 15.1]</t>
+          <t>[14.7, 14.5, 14.3]</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.844675381234297</v>
+        <v>0.9260705911558653</v>
       </c>
       <c r="G59" t="n">
-        <v>1.224087515936692</v>
+        <v>0.9097200517125046</v>
       </c>
       <c r="H59" t="n">
-        <v>8.071363886885157</v>
+        <v>6.285830446737071</v>
       </c>
     </row>
     <row r="60">
@@ -2566,32 +2566,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[15.73, 18.27, 18.77]</t>
+          <t>[15.51, 15.28, 16.05]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[15.5, 15.1, 15.0]</t>
+          <t>[14.5, 14.3, 14.2]</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.843886878136894</v>
+        <v>1.339363971963079</v>
       </c>
       <c r="G60" t="n">
-        <v>2.386112113619367</v>
+        <v>1.27761671822495</v>
       </c>
       <c r="H60" t="n">
-        <v>15.84465029023624</v>
+        <v>8.932225266343597</v>
       </c>
     </row>
     <row r="61">
@@ -2602,32 +2602,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[18.26, 18.76, 16.64]</t>
+          <t>[15.22, 16.0, 15.28]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[15.1, 15.0, 15.1]</t>
+          <t>[14.3, 14.2, 14.0]</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.971452776411701</v>
+        <v>1.380291183269935</v>
       </c>
       <c r="G61" t="n">
-        <v>2.81974625567763</v>
+        <v>1.332716943626081</v>
       </c>
       <c r="H61" t="n">
-        <v>18.7291501732771</v>
+        <v>9.41313788425408</v>
       </c>
     </row>
     <row r="62">
@@ -2638,32 +2638,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.13]</t>
+          <t>[0.25, 0.21, 0.03]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.1663945046437255</v>
+        <v>0.114366326002241</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1561323543031407</v>
+        <v>0.1103708483566488</v>
       </c>
       <c r="H62" t="n">
-        <v>78.06617715157033</v>
+        <v>110.3708483566488</v>
       </c>
     </row>
     <row r="63">
@@ -2674,32 +2674,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0.18, 0.32, 1.0]</t>
+          <t>[0.08, -0.08, -0.17]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.4651059413953378</v>
+        <v>0.1883821116099217</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3119373197002759</v>
+        <v>0.1579524084275381</v>
       </c>
       <c r="H63" t="n">
-        <v>155.968659850138</v>
+        <v>157.952408427538</v>
       </c>
     </row>
     <row r="64">
@@ -2710,32 +2710,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0.34, 1.02, 0.88]</t>
+          <t>[-0.07, -0.15, -0.09]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.6200483120386796</v>
+        <v>0.206642082394299</v>
       </c>
       <c r="G64" t="n">
-        <v>0.54628493799417</v>
+        <v>0.2033383358949286</v>
       </c>
       <c r="H64" t="n">
-        <v>273.142468997085</v>
+        <v>203.3383358949285</v>
       </c>
     </row>
     <row r="65">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0.83, 0.7, 0.69]</t>
+          <t>[-0.02, 0.06, -0.02]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.2]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.5446867437526349</v>
+        <v>0.1476367346810143</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5410308589082321</v>
+        <v>0.127799635088518</v>
       </c>
       <c r="H65" t="n">
-        <v>270.515429454116</v>
+        <v>90.63211739597428</v>
       </c>
     </row>
     <row r="66">
@@ -2782,32 +2782,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0.12, 0.12, -0.07]</t>
+          <t>[0.17, 0.08, 0.08]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.2, 0.1]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.1683017213999847</v>
+        <v>0.08037689606887166</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1436573724608427</v>
+        <v>0.06864318769451705</v>
       </c>
       <c r="H66" t="n">
-        <v>71.82868623042137</v>
+        <v>48.90908880923628</v>
       </c>
     </row>
     <row r="67">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0.19, -0.0, 0.05]</t>
+          <t>[0.02, 0.02, 0.13]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.1]</t>
+          <t>[0.2, 0.1, 0.1]</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.1210246555713456</v>
+        <v>0.1135714820531376</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0855887185970874</v>
+        <v>0.09601849020010667</v>
       </c>
       <c r="H67" t="n">
-        <v>50.63851365935969</v>
+        <v>66.29222061961359</v>
       </c>
     </row>
     <row r="68">
@@ -2854,32 +2854,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[-0.0, 0.06, 0.03]</t>
+          <t>[0.19, 0.31, 0.9]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0.2, 0.1, 0.1]</t>
+          <t>[0.1, 0.1, 0.3]</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.1255578365402664</v>
+        <v>0.3691796318001997</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1055503537282592</v>
+        <v>0.2977873828555871</v>
       </c>
       <c r="H68" t="n">
-        <v>72.21641555561705</v>
+        <v>164.9469015441644</v>
       </c>
     </row>
     <row r="69">
@@ -2890,32 +2890,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0.25, 0.21, 0.03]</t>
+          <t>[0.22, 0.76, 0.65]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.1, 0.3, 0.1]</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.114366326002241</v>
+        <v>0.4206991241426599</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1103708483566488</v>
+        <v>0.3767900329150515</v>
       </c>
       <c r="H69" t="n">
-        <v>110.3708483566488</v>
+        <v>273.8442848010046</v>
       </c>
     </row>
     <row r="70">
@@ -2926,32 +2926,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0.08, -0.08, -0.17]</t>
+          <t>[0.61, 0.51, 0.5]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.3, 0.1, 0.3]</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.1883821116099217</v>
+        <v>0.3180723315259505</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1579524084275381</v>
+        <v>0.3068190544136533</v>
       </c>
       <c r="H70" t="n">
-        <v>157.952408427538</v>
+        <v>192.9036437912964</v>
       </c>
     </row>
     <row r="71">
@@ -2962,32 +2962,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[-0.07, -0.15, -0.09]</t>
+          <t>[0.22, 0.22, 0.03]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.1, 0.3, 0.2]</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.206642082394299</v>
+        <v>0.1279447696329823</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2033383358949286</v>
+        <v>0.1232070792715349</v>
       </c>
       <c r="H71" t="n">
-        <v>203.3383358949285</v>
+        <v>76.89629509096375</v>
       </c>
     </row>
     <row r="72">
@@ -2998,32 +2998,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[14895.41, 13784.78, 14703.92]</t>
+          <t>[14523.4, 14375.55, 15384.44]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[14208.6, 14391.8, 13738.5]</t>
+          <t>[14567.7, 14597.2, 15961.0]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>768.5958515721155</v>
+        <v>357.5423745210212</v>
       </c>
       <c r="G72" t="n">
-        <v>753.0838915522066</v>
+        <v>280.8355264754246</v>
       </c>
       <c r="H72" t="n">
-        <v>5.359568734581103</v>
+        <v>1.811607689996872</v>
       </c>
     </row>
     <row r="73">
@@ -3034,32 +3034,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[13214.13, 14105.14, 13014.79]</t>
+          <t>[14409.14, 15419.93, 14944.51]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[14391.8, 13738.5, 13958.4]</t>
+          <t>[14597.2, 15961.0, 17495.6]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>896.6143463106871</v>
+        <v>1509.547021350471</v>
       </c>
       <c r="G73" t="n">
-        <v>829.3108438117009</v>
+        <v>1093.409719017573</v>
       </c>
       <c r="H73" t="n">
-        <v>5.87062551431149</v>
+        <v>6.419887431825483</v>
       </c>
     </row>
     <row r="74">
@@ -3070,32 +3070,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[15208.09, 14015.28, 15439.55]</t>
+          <t>[15586.93, 15105.99, 15916.73]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[13738.5, 13958.4, 15634.1]</t>
+          <t>[15961.0, 17495.6, 17266.1]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>856.5010903359272</v>
+        <v>1599.060483712399</v>
       </c>
       <c r="G74" t="n">
-        <v>573.6736920641337</v>
+        <v>1371.018087463348</v>
       </c>
       <c r="H74" t="n">
-        <v>4.116258695639399</v>
+        <v>7.939054293830441</v>
       </c>
     </row>
     <row r="75">
@@ -3106,32 +3106,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[12839.84, 14162.63, 12029.91]</t>
+          <t>[15405.07, 16227.84, 15889.75]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[13958.4, 15634.1, 14532.9]</t>
+          <t>[17495.6, 17266.1, 15993.0]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1796.41872411954</v>
+        <v>1348.943545166744</v>
       </c>
       <c r="G75" t="n">
-        <v>1697.673758905323</v>
+        <v>1077.344660043187</v>
       </c>
       <c r="H75" t="n">
-        <v>11.54946214589994</v>
+        <v>6.202578132593263</v>
       </c>
     </row>
     <row r="76">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[15194.73, 12900.74, 13592.03]</t>
+          <t>[18049.57, 17649.9, 16536.36]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[15634.1, 14532.9, 13793.4]</t>
+          <t>[17266.1, 15993.0, 15508.6]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>982.776857541452</v>
+        <v>1213.181511272372</v>
       </c>
       <c r="G76" t="n">
-        <v>757.6329382489766</v>
+        <v>1156.042038181465</v>
       </c>
       <c r="H76" t="n">
-        <v>5.167005644007966</v>
+        <v>7.174929038162238</v>
       </c>
     </row>
     <row r="77">
@@ -3178,32 +3178,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[13214.08, 13916.99, 14450.11]</t>
+          <t>[17011.8, 15944.89, 16657.22]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[14532.9, 13793.4, 14567.7]</t>
+          <t>[15993.0, 15508.6, 19010.0]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>767.7653886252758</v>
+        <v>1501.542325355439</v>
       </c>
       <c r="G77" t="n">
-        <v>519.9993847210529</v>
+        <v>1269.289706047708</v>
       </c>
       <c r="H77" t="n">
-        <v>3.592636901655458</v>
+        <v>7.186676317668568</v>
       </c>
     </row>
     <row r="78">
@@ -3214,32 +3214,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[15087.97, 15647.86, 15475.25]</t>
+          <t>[15153.44, 15841.18, 14820.2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[13793.4, 14567.7, 14597.2]</t>
+          <t>[15508.6, 19010.0, 18345.7]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1097.513044015225</v>
+        <v>2744.490018338204</v>
       </c>
       <c r="G78" t="n">
-        <v>1084.256417006559</v>
+        <v>2349.825931324704</v>
       </c>
       <c r="H78" t="n">
-        <v>7.605103275761989</v>
+        <v>12.72544629686345</v>
       </c>
     </row>
     <row r="79">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[14523.4, 14375.55, 15384.44]</t>
+          <t>[16145.59, 15100.7, 16656.58]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[14567.7, 14597.2, 15961.0]</t>
+          <t>[19010.0, 18345.7, 20423.9]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>357.5423745210212</v>
+        <v>3312.984113916933</v>
       </c>
       <c r="G79" t="n">
-        <v>280.8355264754246</v>
+        <v>3292.244430615957</v>
       </c>
       <c r="H79" t="n">
-        <v>1.811607689996872</v>
+        <v>17.06721346891903</v>
       </c>
     </row>
     <row r="80">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[14409.14, 15419.93, 14944.51]</t>
+          <t>[17285.91, 19032.93, 16355.01]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[14597.2, 15961.0, 17495.6]</t>
+          <t>[18345.7, 20423.9, 20916.3]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1509.547021350471</v>
+        <v>2820.36141100124</v>
       </c>
       <c r="G80" t="n">
-        <v>1093.409719017573</v>
+        <v>2337.34910797101</v>
       </c>
       <c r="H80" t="n">
-        <v>6.419887431825483</v>
+        <v>11.46487036034329</v>
       </c>
     </row>
     <row r="81">
@@ -3322,32 +3322,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[15586.93, 15105.99, 15916.73]</t>
+          <t>[20033.08, 17188.19, 17780.36]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[15961.0, 17495.6, 17266.1]</t>
+          <t>[20423.9, 20916.3, 21832.0]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1599.060483712399</v>
+        <v>3186.815416102521</v>
       </c>
       <c r="G81" t="n">
-        <v>1371.018087463348</v>
+        <v>2723.524735050384</v>
       </c>
       <c r="H81" t="n">
-        <v>7.939054293830441</v>
+        <v>12.76525701105675</v>
       </c>
     </row>
     <row r="82">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[7976.02, 7135.23, 10012.47]</t>
+          <t>[18398.77, 14818.33, 11604.34]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[8077.7, 6406.5, 7596.5]</t>
+          <t>[14534.9, 11659.5, 8246.6]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1458.111897993023</v>
+        <v>3472.854240176253</v>
       </c>
       <c r="G82" t="n">
-        <v>1082.124890961952</v>
+        <v>3460.148438181761</v>
       </c>
       <c r="H82" t="n">
-        <v>14.81242333934475</v>
+        <v>31.46414436481826</v>
       </c>
     </row>
     <row r="83">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[7224.77, 10137.67, 11193.9]</t>
+          <t>[11730.39, 9204.77, 8459.07]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[6406.5, 7596.5, 8548.5]</t>
+          <t>[11659.5, 8246.6, 7127.0]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2169.887424507937</v>
+        <v>948.2499661657671</v>
       </c>
       <c r="G83" t="n">
-        <v>2001.613296008866</v>
+        <v>787.046346350718</v>
       </c>
       <c r="H83" t="n">
-        <v>25.7233810328397</v>
+        <v>10.30584554241735</v>
       </c>
     </row>
     <row r="84">
@@ -3430,32 +3430,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[8998.13, 9945.82, 10313.37]</t>
+          <t>[9149.56, 8408.88, 8722.29]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[7596.5, 8548.5, 11266.8]</t>
+          <t>[8246.6, 7127.0, 7000.5]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1268.345972735568</v>
+        <v>1344.512306484904</v>
       </c>
       <c r="G84" t="n">
-        <v>1250.794192328492</v>
+        <v>1302.212974164006</v>
       </c>
       <c r="H84" t="n">
-        <v>14.41970225425562</v>
+        <v>17.84369994764004</v>
       </c>
     </row>
     <row r="85">
@@ -3466,32 +3466,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[8407.99, 8731.34, 11368.59]</t>
+          <t>[7586.06, 7876.15, 6111.39]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[8548.5, 11266.8, 14618.4]</t>
+          <t>[7127.0, 7000.5, 4617.9]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2381.144573264274</v>
+        <v>1034.088476374497</v>
       </c>
       <c r="G85" t="n">
-        <v>1975.258571970552</v>
+        <v>942.7339053591983</v>
       </c>
       <c r="H85" t="n">
-        <v>15.45947010791367</v>
+        <v>17.09696027990122</v>
       </c>
     </row>
     <row r="86">
@@ -3502,32 +3502,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[8876.2, 11555.46, 13452.49]</t>
+          <t>[7403.53, 5747.94, 5093.95]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[11266.8, 14618.4, 18504.3]</t>
+          <t>[7000.5, 4617.9, 4184.4]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3679.558006979001</v>
+        <v>869.2332283533424</v>
       </c>
       <c r="G86" t="n">
-        <v>3501.787308622276</v>
+        <v>814.2054764841423</v>
       </c>
       <c r="H86" t="n">
-        <v>23.15718163597121</v>
+        <v>17.32155567670922</v>
       </c>
     </row>
     <row r="87">
@@ -3538,32 +3538,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[14636.22, 17004.31, 16919.26]</t>
+          <t>[5437.77, 4821.38, 6674.3]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[14618.4, 18504.3, 14534.9]</t>
+          <t>[4617.9, 4184.4, 6278.0]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1626.391543106273</v>
+        <v>641.611502412789</v>
       </c>
       <c r="G87" t="n">
-        <v>1300.722667873704</v>
+        <v>617.7197011920049</v>
       </c>
       <c r="H87" t="n">
-        <v>8.21081394666955</v>
+        <v>13.09653815828405</v>
       </c>
     </row>
     <row r="88">
@@ -3574,32 +3574,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[16982.9, 16898.51, 13620.31]</t>
+          <t>[4099.84, 5683.64, 6317.49]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[18504.3, 14534.9, 11659.5]</t>
+          <t>[4184.4, 6278.0, 6696.0]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1978.730013921815</v>
+        <v>409.7510092927563</v>
       </c>
       <c r="G88" t="n">
-        <v>1948.609247033418</v>
+        <v>352.4785209036072</v>
       </c>
       <c r="H88" t="n">
-        <v>13.76694036347051</v>
+        <v>5.713696633056096</v>
       </c>
     </row>
     <row r="89">
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[18398.77, 14818.33, 11604.34]</t>
+          <t>[5799.77, 6444.89, 6870.47]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[14534.9, 11659.5, 8246.6]</t>
+          <t>[6278.0, 6696.0, 6999.2]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3472.854240176253</v>
+        <v>320.5912649466111</v>
       </c>
       <c r="G89" t="n">
-        <v>3460.148438181761</v>
+        <v>286.0252486509059</v>
       </c>
       <c r="H89" t="n">
-        <v>31.46414436481826</v>
+        <v>4.402334177789005</v>
       </c>
     </row>
     <row r="90">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[11730.39, 9204.77, 8459.07]</t>
+          <t>[6972.66, 7427.76, 9683.6]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[11659.5, 8246.6, 7127.0]</t>
+          <t>[6696.0, 6999.2, 10690.5]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>948.2499661657671</v>
+        <v>651.6786079124932</v>
       </c>
       <c r="G90" t="n">
-        <v>787.046346350718</v>
+        <v>570.706728053315</v>
       </c>
       <c r="H90" t="n">
-        <v>10.30584554241735</v>
+        <v>6.557780558669268</v>
       </c>
     </row>
     <row r="91">
@@ -3682,32 +3682,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[9149.56, 8408.88, 8722.29]</t>
+          <t>[7135.46, 9305.62, 10947.79]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[8246.6, 7127.0, 7000.5]</t>
+          <t>[6999.2, 10690.5, 13810.0]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1344.512306484904</v>
+        <v>1837.454981428035</v>
       </c>
       <c r="G91" t="n">
-        <v>1302.212974164006</v>
+        <v>1461.118902854042</v>
       </c>
       <c r="H91" t="n">
-        <v>17.84369994764004</v>
+        <v>11.87560227021669</v>
       </c>
     </row>
     <row r="92">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[10133.28, 10820.91, 11928.95]</t>
+          <t>[12047.28, 12156.3, 10495.87]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[9718.4, 10614.4, 12963.7]</t>
+          <t>[12949.8, 13164.9, 10955.9]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>654.5927814684075</v>
+        <v>825.3154621214697</v>
       </c>
       <c r="G92" t="n">
-        <v>552.0464370968263</v>
+        <v>790.3821731434806</v>
       </c>
       <c r="H92" t="n">
-        <v>4.732160795944634</v>
+        <v>6.276518148125872</v>
       </c>
     </row>
     <row r="93">
@@ -3754,32 +3754,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[10662.88, 11754.93, 13022.82]</t>
+          <t>[12453.31, 10749.61, 10918.29]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[10614.4, 12963.7, 12617.3]</t>
+          <t>[13164.9, 10955.9, 11636.6]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>736.6437765623494</v>
+        <v>595.7844211108136</v>
       </c>
       <c r="G93" t="n">
-        <v>554.2577412189161</v>
+        <v>545.3945503833389</v>
       </c>
       <c r="H93" t="n">
-        <v>4.331674434029644</v>
+        <v>4.48697217046873</v>
       </c>
     </row>
     <row r="94">
@@ -3790,32 +3790,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[11739.28, 13004.29, 13881.09]</t>
+          <t>[10942.66, 11113.1, 10188.1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[12963.7, 12617.3, 12366.7]</t>
+          <t>[10955.9, 11636.6, 10530.0]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1146.350304979043</v>
+        <v>361.0741375698387</v>
       </c>
       <c r="G94" t="n">
-        <v>1041.934496004544</v>
+        <v>292.8812257026026</v>
       </c>
       <c r="H94" t="n">
-        <v>8.252620901896751</v>
+        <v>2.622177688491675</v>
       </c>
     </row>
     <row r="95">
@@ -3826,32 +3826,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[13416.85, 14316.01, 15281.97]</t>
+          <t>[11114.82, 10193.72, 9678.81]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[12617.3, 12366.7, 13068.2]</t>
+          <t>[11636.6, 10530.0, 8763.4]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1764.45314970088</v>
+        <v>638.56710961532</v>
       </c>
       <c r="G95" t="n">
-        <v>1654.211168785557</v>
+        <v>591.154236928364</v>
       </c>
       <c r="H95" t="n">
-        <v>13.01322071409707</v>
+        <v>6.041083555526185</v>
       </c>
     </row>
     <row r="96">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[14049.47, 14999.3, 12940.63]</t>
+          <t>[10341.77, 9819.69, 10511.56]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[12366.7, 13068.2, 11662.0]</t>
+          <t>[10530.0, 8763.4, 10359.5]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1652.851230109156</v>
+        <v>625.6476002019225</v>
       </c>
       <c r="G96" t="n">
-        <v>1630.832494937498</v>
+        <v>465.5265186501086</v>
       </c>
       <c r="H96" t="n">
-        <v>13.11613633714862</v>
+        <v>5.102938894252354</v>
       </c>
     </row>
     <row r="97">
@@ -3898,32 +3898,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[14414.0, 12440.25, 12583.9]</t>
+          <t>[9875.97, 10571.95, 11776.32]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[13068.2, 11662.0, 12949.8]</t>
+          <t>[8763.4, 10359.5, 10459.2]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>922.0898973695254</v>
+        <v>1002.957064983594</v>
       </c>
       <c r="G97" t="n">
-        <v>829.9860286961242</v>
+        <v>880.7161526210439</v>
       </c>
       <c r="H97" t="n">
-        <v>6.599085509100773</v>
+        <v>9.113145820080566</v>
       </c>
     </row>
     <row r="98">
@@ -3934,32 +3934,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[12037.76, 12179.59, 12292.07]</t>
+          <t>[10178.4, 11342.13, 12406.74]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[11662.0, 12949.8, 13164.9]</t>
+          <t>[10359.5, 10459.2, 11136.5]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>706.2250930184364</v>
+        <v>899.2343334605728</v>
       </c>
       <c r="G98" t="n">
-        <v>672.9357533958324</v>
+        <v>778.0888728310625</v>
       </c>
       <c r="H98" t="n">
-        <v>5.266594493518078</v>
+        <v>7.198626124366374</v>
       </c>
     </row>
     <row r="99">
@@ -3970,32 +3970,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[12047.28, 12156.3, 10495.87]</t>
+          <t>[11405.88, 12476.05, 13207.11]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[12949.8, 13164.9, 10955.9]</t>
+          <t>[10459.2, 11136.5, 10509.0]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>825.3154621214697</v>
+        <v>1823.037782525937</v>
       </c>
       <c r="G99" t="n">
-        <v>790.3821731434806</v>
+        <v>1661.445710988652</v>
       </c>
       <c r="H99" t="n">
-        <v>6.276518148125872</v>
+        <v>15.58462955047819</v>
       </c>
     </row>
     <row r="100">
@@ -4006,32 +4006,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[12453.31, 10749.61, 10918.29]</t>
+          <t>[12139.88, 12855.49, 13719.74]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[13164.9, 10955.9, 11636.6]</t>
+          <t>[11136.5, 10509.0, 13037.6]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>595.7844211108136</v>
+        <v>1525.136544660152</v>
       </c>
       <c r="G100" t="n">
-        <v>545.3945503833389</v>
+        <v>1344.005686641366</v>
       </c>
       <c r="H100" t="n">
-        <v>4.48697217046873</v>
+        <v>12.1901257429225</v>
       </c>
     </row>
     <row r="101">
@@ -4042,32 +4042,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[10942.66, 11113.1, 10188.1]</t>
+          <t>[12494.07, 13338.17, 11555.14]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[10955.9, 11636.6, 10530.0]</t>
+          <t>[10509.0, 13037.6, 11245.8]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>361.0741375698387</v>
+        <v>1172.819857436786</v>
       </c>
       <c r="G101" t="n">
-        <v>292.8812257026026</v>
+        <v>864.9904363180625</v>
       </c>
       <c r="H101" t="n">
-        <v>2.622177688491675</v>
+        <v>7.981762352781975</v>
       </c>
     </row>
     <row r="102">
@@ -4078,32 +4078,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[52030.1, 48819.97, 55174.11]</t>
+          <t>[53760.51, 51027.17, 51055.51]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[53229.8, 52155.5, 56942.5]</t>
+          <t>[54175.0, 48842.0, 48503.5]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2287.084158354301</v>
+        <v>1954.441230106677</v>
       </c>
       <c r="G102" t="n">
-        <v>2101.207877000093</v>
+        <v>1717.223516690021</v>
       </c>
       <c r="H102" t="n">
-        <v>3.918248966916357</v>
+        <v>3.500182920866191</v>
       </c>
     </row>
     <row r="103">
@@ -4114,32 +4114,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[49934.1, 56419.67, 55173.62]</t>
+          <t>[51419.08, 51440.97, 50840.85]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[52155.5, 56942.5, 52648.1]</t>
+          <t>[48842.0, 48503.5, 46995.1]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1965.215657571484</v>
+        <v>3165.42934484897</v>
       </c>
       <c r="G103" t="n">
-        <v>1756.582091877351</v>
+        <v>3120.098293519045</v>
       </c>
       <c r="H103" t="n">
-        <v>3.324777973487261</v>
+        <v>6.505283949095965</v>
       </c>
     </row>
     <row r="104">
@@ -4150,32 +4150,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[58911.74, 57590.13, 60524.78]</t>
+          <t>[48883.77, 48336.57, 51156.65]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[56942.5, 52648.1, 53358.4]</t>
+          <t>[48503.5, 46995.1, 51088.6]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>5152.9471969179</v>
+        <v>805.9746559652037</v>
       </c>
       <c r="G104" t="n">
-        <v>4692.550554524804</v>
+        <v>596.5996352153039</v>
       </c>
       <c r="H104" t="n">
-        <v>8.758619661594551</v>
+        <v>1.257237440478169</v>
       </c>
     </row>
     <row r="105">
@@ -4186,32 +4186,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[55682.47, 58536.39, 59668.62]</t>
+          <t>[47960.75, 50767.31, 44957.18]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[52648.1, 53358.4, 53060.3]</t>
+          <t>[46995.1, 51088.6, 50601.1]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5153.927377949857</v>
+        <v>3311.067550268475</v>
       </c>
       <c r="G105" t="n">
-        <v>4940.227899420216</v>
+        <v>2310.286524466168</v>
       </c>
       <c r="H105" t="n">
-        <v>9.307343199278632</v>
+        <v>4.612475273243599</v>
       </c>
     </row>
     <row r="106">
@@ -4222,32 +4222,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[55373.37, 56472.72, 58541.71]</t>
+          <t>[49752.21, 44064.32, 41583.36]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[53358.4, 53060.3, 54038.5]</t>
+          <t>[51088.6, 50601.1, 41905.6]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3463.312328815985</v>
+        <v>3856.562311313947</v>
       </c>
       <c r="G106" t="n">
-        <v>3310.199346269001</v>
+        <v>2731.803386891918</v>
       </c>
       <c r="H106" t="n">
-        <v>6.180279318491163</v>
+        <v>5.434350771062058</v>
       </c>
     </row>
     <row r="107">
@@ -4258,32 +4258,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[54434.03, 56448.57, 56133.08]</t>
+          <t>[45238.56, 42682.33, 48126.62]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[53060.3, 54038.5, 54175.0]</t>
+          <t>[50601.1, 41905.6, 46816.9]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1960.413846357073</v>
+        <v>3218.463957603275</v>
       </c>
       <c r="G107" t="n">
-        <v>1913.960835052218</v>
+        <v>2482.996886359191</v>
       </c>
       <c r="H107" t="n">
-        <v>3.554425337590547</v>
+        <v>5.082911732147783</v>
       </c>
     </row>
     <row r="108">
@@ -4294,32 +4294,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[55031.61, 54736.77, 51947.08]</t>
+          <t>[47697.05, 53730.11, 52272.15]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[54038.5, 54175.0, 48842.0]</t>
+          <t>[41905.6, 46816.9, 54373.4]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1909.920792700474</v>
+        <v>5346.293466056549</v>
       </c>
       <c r="G108" t="n">
-        <v>1553.32268585977</v>
+        <v>4935.300826020684</v>
       </c>
       <c r="H108" t="n">
-        <v>3.077383008084091</v>
+        <v>10.81705988201999</v>
       </c>
     </row>
     <row r="109">
@@ -4330,32 +4330,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[53760.51, 51027.17, 51055.51]</t>
+          <t>[47255.5, 46017.36, 48273.03]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[54175.0, 48842.0, 48503.5]</t>
+          <t>[46816.9, 54373.4, 54243.7]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1954.441230106677</v>
+        <v>5934.776272956889</v>
       </c>
       <c r="G109" t="n">
-        <v>1717.223516690021</v>
+        <v>4921.769685634276</v>
       </c>
       <c r="H109" t="n">
-        <v>3.500182920866191</v>
+        <v>9.103947258354921</v>
       </c>
     </row>
     <row r="110">
@@ -4366,32 +4366,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[51419.08, 51440.97, 50840.85]</t>
+          <t>[45596.19, 47832.02, 48711.96]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[48842.0, 48503.5, 46995.1]</t>
+          <t>[54373.4, 54243.7, 56042.2]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3165.42934484897</v>
+        <v>7569.267949184352</v>
       </c>
       <c r="G110" t="n">
-        <v>3120.098293519045</v>
+        <v>7506.376002321063</v>
       </c>
       <c r="H110" t="n">
-        <v>6.505283949095965</v>
+        <v>13.68082075782134</v>
       </c>
     </row>
     <row r="111">
@@ -4402,32 +4402,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[48883.77, 48336.57, 51156.65]</t>
+          <t>[56962.59, 57932.48, 59932.35]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[48503.5, 46995.1, 51088.6]</t>
+          <t>[54243.7, 56042.2, 54984.8]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>805.9746559652037</v>
+        <v>3437.235822544116</v>
       </c>
       <c r="G111" t="n">
-        <v>596.5996352153039</v>
+        <v>3185.573584843994</v>
       </c>
       <c r="H111" t="n">
-        <v>1.257237440478169</v>
+        <v>5.794450831727291</v>
       </c>
     </row>
     <row r="112">
@@ -4438,32 +4438,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[26603.87, 25024.41, 41124.92]</t>
+          <t>[33861.77, 29400.36, 22854.76]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[35614.2, 30979.0, 37989.2]</t>
+          <t>[34474.8, 33915.9, 33318.5]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6492.966739935478</v>
+        <v>6589.279967307742</v>
       </c>
       <c r="G112" t="n">
-        <v>6033.544095641486</v>
+        <v>5197.438116363463</v>
       </c>
       <c r="H112" t="n">
-        <v>17.59180607124963</v>
+        <v>15.49911269808984</v>
       </c>
     </row>
     <row r="113">
@@ -4474,32 +4474,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[30917.92, 50705.83, 46347.01]</t>
+          <t>[29809.33, 23169.78, 30073.68]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[30979.0, 37989.2, 33245.4]</t>
+          <t>[33915.9, 33318.5, 33853.9]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>10541.48203460509</v>
+        <v>6687.063451390756</v>
       </c>
       <c r="G113" t="n">
-        <v>8626.437707233474</v>
+        <v>6011.836604231313</v>
       </c>
       <c r="H113" t="n">
-        <v>24.36008800603215</v>
+        <v>17.91136230161721</v>
       </c>
     </row>
     <row r="114">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[50781.05, 46415.55, 43502.59]</t>
+          <t>[25599.78, 33195.85, 35532.19]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[37989.2, 33245.4, 25427.0]</t>
+          <t>[33318.5, 33853.9, 31412.9]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>14875.16064944568</v>
+        <v>5065.580304232588</v>
       </c>
       <c r="G114" t="n">
-        <v>14679.19647364488</v>
+        <v>4165.356841521737</v>
       </c>
       <c r="H114" t="n">
-        <v>48.1251528426894</v>
+        <v>12.74122192094778</v>
       </c>
     </row>
     <row r="115">
@@ -4546,32 +4546,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[37849.97, 35533.49, 37604.71]</t>
+          <t>[41068.71, 43873.64, 32779.05]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[33245.4, 25427.0, 28739.0]</t>
+          <t>[33853.9, 31412.9, 33270.7]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>8204.553147900462</v>
+        <v>8317.954949667326</v>
       </c>
       <c r="G115" t="n">
-        <v>7858.9251593869</v>
+        <v>6722.398502579</v>
       </c>
       <c r="H115" t="n">
-        <v>28.14879960728712</v>
+        <v>20.81896945758359</v>
       </c>
     </row>
     <row r="116">
@@ -4582,32 +4582,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[32236.89, 34139.96, 33945.52]</t>
+          <t>[37779.94, 28266.98, 26368.36]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[25427.0, 28739.0, 33188.9]</t>
+          <t>[31412.9, 33270.7, 25198.0]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5037.110570599506</v>
+        <v>4723.916701541445</v>
       </c>
       <c r="G116" t="n">
-        <v>4322.491328861765</v>
+        <v>4180.374172497774</v>
       </c>
       <c r="H116" t="n">
-        <v>15.95167011826129</v>
+        <v>13.31765075624914</v>
       </c>
     </row>
     <row r="117">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[28370.74, 28254.3, 29873.41]</t>
+          <t>[24486.58, 22869.02, 36526.16]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[28739.0, 33188.9, 34474.8]</t>
+          <t>[33270.7, 25198.0, 28343.3]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3901.226935916704</v>
+        <v>7060.315611833089</v>
       </c>
       <c r="G117" t="n">
-        <v>3301.418560993265</v>
+        <v>6431.987495824531</v>
       </c>
       <c r="H117" t="n">
-        <v>9.832249427497882</v>
+        <v>21.50507392409636</v>
       </c>
     </row>
     <row r="118">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[28541.16, 30173.46, 26224.5]</t>
+          <t>[28640.66, 45657.59, 41577.95]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[33188.9, 34474.8, 33915.9]</t>
+          <t>[25198.0, 28343.3, 34878.5]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>5752.119035328088</v>
+        <v>10901.36346778525</v>
       </c>
       <c r="G118" t="n">
-        <v>5546.82580162037</v>
+        <v>9152.131988233084</v>
       </c>
       <c r="H118" t="n">
-        <v>16.38617203906853</v>
+        <v>31.31938428213014</v>
       </c>
     </row>
     <row r="119">
@@ -4690,32 +4690,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[33861.77, 29400.36, 22854.76]</t>
+          <t>[41676.57, 37980.45, 34926.58]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[34474.8, 33915.9, 33318.5]</t>
+          <t>[28343.3, 34878.5, 35445.3]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>6589.279967307742</v>
+        <v>7909.22006864183</v>
       </c>
       <c r="G119" t="n">
-        <v>5197.438116363463</v>
+        <v>5651.312683153047</v>
       </c>
       <c r="H119" t="n">
-        <v>15.49911269808984</v>
+        <v>19.13302461540189</v>
       </c>
     </row>
     <row r="120">
@@ -4726,32 +4726,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[29809.33, 23169.78, 30073.68]</t>
+          <t>[29313.6, 28091.85, 31043.73]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[33915.9, 33318.5, 33853.9]</t>
+          <t>[34878.5, 35445.3, 33353.5]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>6687.063451390756</v>
+        <v>5488.663551230188</v>
       </c>
       <c r="G120" t="n">
-        <v>6011.836604231313</v>
+        <v>5076.036990654376</v>
       </c>
       <c r="H120" t="n">
-        <v>17.91136230161721</v>
+        <v>14.54203513133118</v>
       </c>
     </row>
     <row r="121">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[25599.78, 33195.85, 35532.19]</t>
+          <t>[32197.62, 35663.87, 37351.15]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[33318.5, 33853.9, 31412.9]</t>
+          <t>[35445.3, 33353.5, 32197.3]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5065.580304232588</v>
+        <v>3761.534787907096</v>
       </c>
       <c r="G121" t="n">
-        <v>4165.356841521737</v>
+        <v>3570.635144285249</v>
       </c>
       <c r="H121" t="n">
-        <v>12.74122192094778</v>
+        <v>10.69884482469035</v>
       </c>
     </row>
     <row r="122">
@@ -4798,32 +4798,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[351.73, 383.65, 389.44]</t>
+          <t>[799.89, 868.09, 743.6]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[307.6, 308.7, 328.6]</t>
+          <t>[784.7, 863.1, 747.7]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>61.28160082514783</v>
+        <v>9.532275888003216</v>
       </c>
       <c r="G122" t="n">
-        <v>59.97318723734687</v>
+        <v>8.095320879260802</v>
       </c>
       <c r="H122" t="n">
-        <v>19.04683003519926</v>
+        <v>1.021005590804235</v>
       </c>
     </row>
     <row r="123">
@@ -4834,32 +4834,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[335.94, 341.46, 564.69]</t>
+          <t>[851.87, 729.79, 649.43]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[308.7, 328.6, 588.4]</t>
+          <t>[863.1, 747.7, 671.1]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>22.13328377350131</v>
+        <v>17.47610494159173</v>
       </c>
       <c r="G123" t="n">
-        <v>21.27039099506601</v>
+        <v>16.93479320961467</v>
       </c>
       <c r="H123" t="n">
-        <v>5.589140651976034</v>
+        <v>2.308233888122047</v>
       </c>
     </row>
     <row r="124">
@@ -4870,32 +4870,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[313.98, 519.67, 578.54]</t>
+          <t>[739.29, 657.84, 665.01]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[328.6, 588.4, 620.5]</t>
+          <t>[747.7, 671.1, 695.8]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>47.25082989270813</v>
+        <v>19.95550065521198</v>
       </c>
       <c r="G124" t="n">
-        <v>41.76990849176828</v>
+        <v>17.48716402547181</v>
       </c>
       <c r="H124" t="n">
-        <v>7.630862383050744</v>
+        <v>2.50864322645318</v>
       </c>
     </row>
     <row r="125">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[543.63, 604.98, 683.26]</t>
+          <t>[665.18, 672.39, 318.51]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[588.4, 620.5, 861.5]</t>
+          <t>[671.1, 695.8, 259.0]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>106.4821225304245</v>
+        <v>37.07859251510111</v>
       </c>
       <c r="G125" t="n">
-        <v>79.51021697232363</v>
+        <v>29.6125803439593</v>
       </c>
       <c r="H125" t="n">
-        <v>10.26647936904906</v>
+        <v>9.074311188414423</v>
       </c>
     </row>
     <row r="126">
@@ -4942,32 +4942,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[654.35, 738.52, 805.71]</t>
+          <t>[678.26, 321.28, 347.78]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[620.5, 861.5, 797.3]</t>
+          <t>[695.8, 259.0, 356.7]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>73.80363054997383</v>
+        <v>37.70791245631631</v>
       </c>
       <c r="G126" t="n">
-        <v>55.08012846290986</v>
+        <v>29.57767263749846</v>
       </c>
       <c r="H126" t="n">
-        <v>6.928417333509302</v>
+        <v>9.688685839819243</v>
       </c>
     </row>
     <row r="127">
@@ -4978,32 +4978,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[700.63, 764.75, 766.34]</t>
+          <t>[329.46, 356.59, 363.87]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[861.5, 797.3, 784.7]</t>
+          <t>[259.0, 356.7, 427.2]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>95.35033675426575</v>
+        <v>54.69625558470478</v>
       </c>
       <c r="G127" t="n">
-        <v>70.59191359005858</v>
+        <v>44.6336881822541</v>
       </c>
       <c r="H127" t="n">
-        <v>8.364999277985143</v>
+        <v>14.02017554152325</v>
       </c>
     </row>
     <row r="128">
@@ -5014,32 +5014,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[938.68, 938.94, 1017.5]</t>
+          <t>[280.89, 287.24, 479.58]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[797.3, 784.7, 863.1]</t>
+          <t>[356.7, 427.2, 681.7]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>150.1273667827102</v>
+        <v>148.5372716564607</v>
       </c>
       <c r="G128" t="n">
-        <v>150.0033277230231</v>
+        <v>139.2991093274834</v>
       </c>
       <c r="H128" t="n">
-        <v>18.42534706463015</v>
+        <v>27.88889229320534</v>
       </c>
     </row>
     <row r="129">
@@ -5050,32 +5050,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[799.89, 868.09, 743.6]</t>
+          <t>[357.21, 595.31, 658.57]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[784.7, 863.1, 747.7]</t>
+          <t>[427.2, 681.7, 737.5]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>9.532275888003216</v>
+        <v>78.7219287135762</v>
       </c>
       <c r="G129" t="n">
-        <v>8.095320879260802</v>
+        <v>78.43606126287699</v>
       </c>
       <c r="H129" t="n">
-        <v>1.021005590804235</v>
+        <v>13.2527924032257</v>
       </c>
     </row>
     <row r="130">
@@ -5086,32 +5086,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[851.87, 729.79, 649.43]</t>
+          <t>[710.82, 785.25, 903.59]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[863.1, 747.7, 671.1]</t>
+          <t>[681.7, 737.5, 837.8]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>17.47610494159173</v>
+        <v>49.85201579450954</v>
       </c>
       <c r="G130" t="n">
-        <v>16.93479320961467</v>
+        <v>47.5508967772026</v>
       </c>
       <c r="H130" t="n">
-        <v>2.308233888122047</v>
+        <v>6.199326556179852</v>
       </c>
     </row>
     <row r="131">
@@ -5122,32 +5122,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[739.29, 657.84, 665.01]</t>
+          <t>[753.33, 867.15, 929.7]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[747.7, 671.1, 695.8]</t>
+          <t>[737.5, 837.8, 808.9]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>19.95550065521198</v>
+        <v>72.35395946455274</v>
       </c>
       <c r="G131" t="n">
-        <v>17.48716402547181</v>
+        <v>55.32910473674895</v>
       </c>
       <c r="H131" t="n">
-        <v>2.50864322645318</v>
+        <v>6.861491959158419</v>
       </c>
     </row>
     <row r="132">
@@ -5158,32 +5158,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[38.88, 25.89, 40.65]</t>
+          <t>[64.4, 65.98, 63.1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[33.7, 28.1, 41.6]</t>
+          <t>[64.1, 62.7, 69.0]</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3.296461149751441</v>
+        <v>3.900293658632303</v>
       </c>
       <c r="G132" t="n">
-        <v>2.779871525849977</v>
+        <v>3.161477095738552</v>
       </c>
       <c r="H132" t="n">
-        <v>8.50624978016552</v>
+        <v>4.752498705815567</v>
       </c>
     </row>
     <row r="133">
@@ -5194,32 +5194,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[22.44, 35.35, 39.7]</t>
+          <t>[65.67, 62.81, 53.42]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>[28.1, 41.6, 57.8]</t>
+          <t>[62.7, 69.0, 48.5]</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>11.52875572407125</v>
+        <v>4.879184584000971</v>
       </c>
       <c r="G133" t="n">
-        <v>10.00225743819472</v>
+        <v>4.696498761990557</v>
       </c>
       <c r="H133" t="n">
-        <v>22.15652507775515</v>
+        <v>7.956450196595304</v>
       </c>
     </row>
     <row r="134">
@@ -5230,32 +5230,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[43.99, 49.28, 47.23]</t>
+          <t>[60.01, 51.06, 52.97]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>[41.6, 57.8, 57.6]</t>
+          <t>[69.0, 48.5, 41.1]</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>7.871072543047612</v>
+        <v>8.723164144058881</v>
       </c>
       <c r="G134" t="n">
-        <v>7.094758831931768</v>
+        <v>7.806415331926476</v>
       </c>
       <c r="H134" t="n">
-        <v>12.83286995818391</v>
+        <v>15.72958750740863</v>
       </c>
     </row>
     <row r="135">
@@ -5266,32 +5266,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[46.64, 44.73, 57.36]</t>
+          <t>[58.58, 60.69, 56.28]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[57.8, 57.6, 97.3]</t>
+          <t>[48.5, 41.1, 30.2]</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>25.07095714188838</v>
+        <v>19.7099983132873</v>
       </c>
       <c r="G135" t="n">
-        <v>21.32498601932967</v>
+        <v>18.58284713735562</v>
       </c>
       <c r="H135" t="n">
-        <v>27.56892067969949</v>
+        <v>51.5996115046465</v>
       </c>
     </row>
     <row r="136">
@@ -5302,32 +5302,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[55.25, 70.66, 86.13]</t>
+          <t>[50.44, 46.83, 31.91]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>[57.6, 97.3, 93.4]</t>
+          <t>[41.1, 30.2, 25.9]</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>15.9978621275302</v>
+        <v>11.54678326110767</v>
       </c>
       <c r="G136" t="n">
-        <v>12.08372040782737</v>
+        <v>10.66121097244259</v>
       </c>
       <c r="H136" t="n">
-        <v>13.07683851516172</v>
+        <v>33.67022065085698</v>
       </c>
     </row>
     <row r="137">
@@ -5338,32 +5338,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[73.61, 89.67, 61.71]</t>
+          <t>[38.29, 26.08, 40.71]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[97.3, 93.4, 64.1]</t>
+          <t>[30.2, 25.9, 37.9]</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>13.91616457026307</v>
+        <v>4.946285141359136</v>
       </c>
       <c r="G137" t="n">
-        <v>9.935843264536564</v>
+        <v>3.69468107307303</v>
       </c>
       <c r="H137" t="n">
-        <v>10.68852900955348</v>
+        <v>11.63577371605693</v>
       </c>
     </row>
     <row r="138">
@@ -5374,32 +5374,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[118.18, 81.23, 83.04]</t>
+          <t>[20.58, 32.3, 37.1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>[93.4, 64.1, 62.7]</t>
+          <t>[25.9, 37.9, 52.2]</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>20.98637186908156</v>
+        <v>9.789266551461147</v>
       </c>
       <c r="G138" t="n">
-        <v>20.75063257607839</v>
+        <v>8.670548771976678</v>
       </c>
       <c r="H138" t="n">
-        <v>28.56582923920092</v>
+        <v>21.40857338915665</v>
       </c>
     </row>
     <row r="139">
@@ -5410,32 +5410,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[64.4, 65.98, 63.1]</t>
+          <t>[40.36, 46.25, 44.54]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[64.1, 62.7, 69.0]</t>
+          <t>[37.9, 52.2, 54.3]</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3.900293658632303</v>
+        <v>6.753638987003377</v>
       </c>
       <c r="G139" t="n">
-        <v>3.161477095738552</v>
+        <v>6.060240686840629</v>
       </c>
       <c r="H139" t="n">
-        <v>4.752498705815567</v>
+        <v>11.96217694739026</v>
       </c>
     </row>
     <row r="140">
@@ -5446,32 +5446,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[65.67, 62.81, 53.42]</t>
+          <t>[43.45, 41.86, 55.27]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[62.7, 69.0, 48.5]</t>
+          <t>[52.2, 54.3, 88.0]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4.879184584000971</v>
+        <v>20.83588032152033</v>
       </c>
       <c r="G140" t="n">
-        <v>4.696498761990557</v>
+        <v>17.97119120151131</v>
       </c>
       <c r="H140" t="n">
-        <v>7.956450196595304</v>
+        <v>25.61793657562626</v>
       </c>
     </row>
     <row r="141">
@@ -5482,32 +5482,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[60.01, 51.06, 52.97]</t>
+          <t>[50.23, 66.16, 78.83]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>[69.0, 48.5, 41.1]</t>
+          <t>[54.3, 88.0, 87.8]</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>8.723164144058881</v>
+        <v>13.83220178821245</v>
       </c>
       <c r="G141" t="n">
-        <v>7.806415331926476</v>
+        <v>11.62582781045852</v>
       </c>
       <c r="H141" t="n">
-        <v>15.72958750740863</v>
+        <v>14.17537931004053</v>
       </c>
     </row>
     <row r="142">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[7394.58, 6881.73, 5780.21]</t>
+          <t>[5769.68, 5268.55, 4233.82]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[6902.5, 7055.3, 6256.2]</t>
+          <t>[6256.2, 5516.8, 4175.4]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>407.7755334337431</v>
+        <v>317.143030289603</v>
       </c>
       <c r="G142" t="n">
-        <v>380.5484473405022</v>
+        <v>264.3955841588943</v>
       </c>
       <c r="H142" t="n">
-        <v>5.732507907677347</v>
+        <v>4.558535209634957</v>
       </c>
     </row>
     <row r="143">
@@ -5554,32 +5554,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[6529.03, 5495.72, 5026.43]</t>
+          <t>[5582.19, 4479.21, 3525.32]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[7055.3, 6256.2, 5516.8]</t>
+          <t>[5516.8, 4175.4, 3304.7]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>604.3625674304423</v>
+        <v>220.0394247805045</v>
       </c>
       <c r="G143" t="n">
-        <v>592.376379500055</v>
+        <v>196.6089386987075</v>
       </c>
       <c r="H143" t="n">
-        <v>9.501216447436338</v>
+        <v>5.045850085919699</v>
       </c>
     </row>
     <row r="144">
@@ -5590,32 +5590,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[5769.68, 5268.55, 4233.82]</t>
+          <t>[4439.41, 3495.22, 3540.24]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[6256.2, 5516.8, 4175.4]</t>
+          <t>[4175.4, 3304.7, 3916.9]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>317.143030289603</v>
+        <v>287.4410890197734</v>
       </c>
       <c r="G144" t="n">
-        <v>264.3955841588943</v>
+        <v>277.0604234568385</v>
       </c>
       <c r="H144" t="n">
-        <v>4.558535209634957</v>
+        <v>7.234715716147115</v>
       </c>
     </row>
     <row r="145">
@@ -5626,32 +5626,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[5582.19, 4479.21, 3525.32]</t>
+          <t>[3367.15, 3414.21, 2338.56]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[5516.8, 4175.4, 3304.7]</t>
+          <t>[3304.7, 3916.9, 2149.0]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>220.0394247805045</v>
+        <v>312.2644173113578</v>
       </c>
       <c r="G145" t="n">
-        <v>196.6089386987075</v>
+        <v>251.5666800336991</v>
       </c>
       <c r="H145" t="n">
-        <v>5.045850085919699</v>
+        <v>7.848167240880004</v>
       </c>
     </row>
     <row r="146">
@@ -5662,1472 +5662,2012 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[4439.41, 3495.22, 3540.24]</t>
+          <t>[3376.29, 2313.5, 3048.29]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[4175.4, 3304.7, 3916.9]</t>
+          <t>[3916.9, 2149.0, 3322.2]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>287.4410890197734</v>
+        <v>362.5583733888768</v>
       </c>
       <c r="G146" t="n">
-        <v>277.0604234568385</v>
+        <v>326.3403014126256</v>
       </c>
       <c r="H146" t="n">
-        <v>7.234715716147115</v>
+        <v>9.90052452242567</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[29874.53, 24053.84, 25579.47]</t>
+          <t>[2489.56, 3272.19, 4754.66]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[28495.5, 26057.7, 27169.4]</t>
+          <t>[2149.0, 3322.2, 4423.2]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1677.80500189007</v>
+        <v>275.892728797228</v>
       </c>
       <c r="G147" t="n">
-        <v>1657.610158038638</v>
+        <v>240.6769178219006</v>
       </c>
       <c r="H147" t="n">
-        <v>6.127168670293623</v>
+        <v>8.282118501237576</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[23503.39, 25022.91, 24942.31]</t>
+          <t>[3079.09, 4483.12, 4940.7]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[26057.7, 27169.4, 29416.8]</t>
+          <t>[3322.2, 4423.2, 5159.2]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3222.474520499679</v>
+        <v>191.8637248851975</v>
       </c>
       <c r="G148" t="n">
-        <v>3058.432003053109</v>
+        <v>173.8443183756297</v>
       </c>
       <c r="H148" t="n">
-        <v>10.97119805073871</v>
+        <v>4.302530460752881</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[26176.13, 26047.13, 28054.62]</t>
+          <t>[4591.96, 5056.4, 7059.37]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[27169.4, 29416.8, 29285.2]</t>
+          <t>[4423.2, 5159.2, 5802.4]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2149.077537868907</v>
+        <v>734.6265531866555</v>
       </c>
       <c r="G149" t="n">
-        <v>1864.508316645552</v>
+        <v>509.5104264693597</v>
       </c>
       <c r="H149" t="n">
-        <v>6.437609710459369</v>
+        <v>9.156946100837555</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[26485.2, 28512.34, 28964.84]</t>
+          <t>[4997.82, 6980.39, 7347.75]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[29416.8, 29285.2, 27011.6]</t>
+          <t>[5159.2, 5802.4, 6556.6]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2082.205963117992</v>
+        <v>824.5437378908156</v>
       </c>
       <c r="G150" t="n">
-        <v>1885.901828204122</v>
+        <v>710.1724008106706</v>
       </c>
       <c r="H150" t="n">
-        <v>6.611983127656072</v>
+        <v>11.83206673398708</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[29964.68, 30386.85, 29784.32]</t>
+          <t>[7048.75, 7415.51, 7116.61]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[29285.2, 27011.6, 27657.0]</t>
+          <t>[5802.4, 6556.6, 7458.2]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2336.628055033444</v>
+        <v>895.8776216090599</v>
       </c>
       <c r="G151" t="n">
-        <v>2060.682225825894</v>
+        <v>815.6159371328118</v>
       </c>
       <c r="H151" t="n">
-        <v>7.502519442757348</v>
+        <v>13.0532839564847</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[2009.95, 1530.38, 1281.51]</t>
+          <t>[26176.13, 26047.13, 28054.62]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[1957.4, 1310.4, 973.5]</t>
+          <t>[27169.4, 29416.8, 29285.2]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>220.6226585503726</v>
+        <v>2149.077537868907</v>
       </c>
       <c r="G152" t="n">
-        <v>193.5126175837378</v>
+        <v>1864.508316645552</v>
       </c>
       <c r="H152" t="n">
-        <v>17.03710851899165</v>
+        <v>6.437609710459369</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[1510.64, 1265.83, 1775.03]</t>
+          <t>[26485.2, 28512.34, 28964.84]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[1310.4, 973.5, 1757.9]</t>
+          <t>[29416.8, 29285.2, 27011.6]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>204.812335525809</v>
+        <v>2082.205963117992</v>
       </c>
       <c r="G153" t="n">
-        <v>169.8981488865933</v>
+        <v>1885.901828204122</v>
       </c>
       <c r="H153" t="n">
-        <v>15.42785210077351</v>
+        <v>6.611983127656072</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[1188.77, 1671.43, 1384.2]</t>
+          <t>[29964.68, 30386.85, 29784.32]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[973.5, 1757.9, 961.6]</t>
+          <t>[29285.2, 27011.6, 27657.0]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>278.3337113686409</v>
+        <v>2336.628055033444</v>
       </c>
       <c r="G154" t="n">
-        <v>241.4477420326985</v>
+        <v>2060.682225825894</v>
       </c>
       <c r="H154" t="n">
-        <v>23.65991848404378</v>
+        <v>7.502519442757348</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[1500.18, 1246.62, 1162.12]</t>
+          <t>[30055.48, 29462.87, 26096.24]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[1757.9, 961.6, 806.3]</t>
+          <t>[27011.6, 27657.0, 25193.8]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>302.357912921742</v>
+        <v>2108.771239447364</v>
       </c>
       <c r="G155" t="n">
-        <v>299.5184254809302</v>
+        <v>1917.395779860771</v>
       </c>
       <c r="H155" t="n">
-        <v>29.47679142632215</v>
+        <v>7.126764348398132</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[1350.32, 1256.03, 1722.44]</t>
+          <t>[28114.24, 24937.12, 27263.12]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[961.6, 806.3, 1780.6]</t>
+          <t>[27657.0, 25193.8, 28661.9]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>344.8376594889358</v>
+        <v>862.4663113497949</v>
       </c>
       <c r="G156" t="n">
-        <v>298.8676339326936</v>
+        <v>704.2335058986488</v>
       </c>
       <c r="H156" t="n">
-        <v>33.1556656643154</v>
+        <v>2.517450409155532</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[14719.8, 14141.61, 15892.21]</t>
+          <t>[24758.26, 27075.43, 27872.5]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[16000.7, 15324.7, 16631.1]</t>
+          <t>[25193.8, 28661.9, 27089.7]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1093.368267567577</v>
+        <v>1051.881444238632</v>
       </c>
       <c r="G157" t="n">
-        <v>1067.625629344426</v>
+        <v>934.9384429606968</v>
       </c>
       <c r="H157" t="n">
-        <v>6.722742637191757</v>
+        <v>3.384518866895773</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[15360.96, 17247.82, 18824.91]</t>
+          <t>[27277.07, 28076.24, 28541.71]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[15324.7, 16631.1, 16747.1]</t>
+          <t>[28661.9, 27089.7, 29787.1]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1251.525714487321</v>
+        <v>1216.829825154681</v>
       </c>
       <c r="G158" t="n">
-        <v>910.2624192020309</v>
+        <v>1205.58869264366</v>
       </c>
       <c r="H158" t="n">
-        <v>5.450603477200105</v>
+        <v>4.218117157259721</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[17209.06, 18782.03, 20437.71]</t>
+          <t>[28680.31, 29129.58, 29085.91]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[16631.1, 16747.1, 17414.0]</t>
+          <t>[27089.7, 29787.1, 27042.1]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2130.553464729001</v>
+        <v>1542.673400742697</v>
       </c>
       <c r="G159" t="n">
-        <v>1878.865936192011</v>
+        <v>1430.646261748243</v>
       </c>
       <c r="H159" t="n">
-        <v>10.99659217661112</v>
+        <v>5.212305470958551</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[18157.21, 19762.17, 20572.37]</t>
+          <t>[28432.01, 28414.67, 29920.28]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[16747.1, 17414.0, 18832.4]</t>
+          <t>[29787.1, 27042.1, 28008.8]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1873.484971260148</v>
+        <v>1567.796416295621</v>
       </c>
       <c r="G160" t="n">
-        <v>1832.752316591989</v>
+        <v>1546.378337614498</v>
       </c>
       <c r="H160" t="n">
-        <v>10.38122646398975</v>
+        <v>5.483160475078499</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[18239.78, 19001.91, 19508.42]</t>
+          <t>[28974.63, 30478.71, 25577.06]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[17414.0, 18832.4, 18654.7]</t>
+          <t>[27042.1, 28008.8, 27987.2]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>692.6978022529947</v>
+        <v>2283.557150015883</v>
       </c>
       <c r="G161" t="n">
-        <v>616.3373222675473</v>
+        <v>2270.859851429035</v>
       </c>
       <c r="H161" t="n">
-        <v>3.406196842647741</v>
+        <v>8.192096377394019</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[18745.89, 19592.8, 19185.22]</t>
+          <t>[1188.77, 1671.43, 1384.2]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[18832.4, 18654.7, 18689.8]</t>
+          <t>[973.5, 1757.9, 961.6]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>614.5363080505111</v>
+        <v>278.3337113686409</v>
       </c>
       <c r="G162" t="n">
-        <v>506.6789606571086</v>
+        <v>241.4477420326985</v>
       </c>
       <c r="H162" t="n">
-        <v>2.712971614448801</v>
+        <v>23.65991848404378</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[19702.41, 19309.68, 19135.57]</t>
+          <t>[1500.18, 1246.62, 1162.12]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[18654.7, 18689.8, 18071.9]</t>
+          <t>[1757.9, 961.6, 806.3]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>933.3326935682351</v>
+        <v>302.357912921742</v>
       </c>
       <c r="G163" t="n">
-        <v>910.4182017229008</v>
+        <v>299.5184254809302</v>
       </c>
       <c r="H163" t="n">
-        <v>4.939581976092188</v>
+        <v>29.47679142632215</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[18430.67, 18766.49, 16041.67]</t>
+          <t>[1350.32, 1256.03, 1722.44]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[18689.8, 18071.9, 16535.5]</t>
+          <t>[961.6, 806.3, 1780.6]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>514.2848947570593</v>
+        <v>344.8376594889358</v>
       </c>
       <c r="G164" t="n">
-        <v>482.515991877189</v>
+        <v>298.8676339326936</v>
       </c>
       <c r="H164" t="n">
-        <v>2.738810167041788</v>
+        <v>33.1556656643154</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[19028.16, 16263.23, 15187.91]</t>
+          <t>[1088.54, 1500.24, 1073.42]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[18071.9, 16535.5, 15899.2]</t>
+          <t>[806.3, 1780.6, 1621.8]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>705.8115482918855</v>
+        <v>391.1427974139859</v>
       </c>
       <c r="G165" t="n">
-        <v>646.6091091319771</v>
+        <v>370.3258813960331</v>
       </c>
       <c r="H165" t="n">
-        <v>3.803929659893588</v>
+        <v>28.18751136345722</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[16145.85, 14971.02, 14953.65]</t>
+          <t>[1240.72, 892.62, 848.27]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[16535.5, 15899.2, 14834.9]</t>
+          <t>[1780.6, 1621.8, 1907.1]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>585.2187383693424</v>
+        <v>805.0477057695509</v>
       </c>
       <c r="G166" t="n">
-        <v>478.8606781337191</v>
+        <v>775.9655392990477</v>
       </c>
       <c r="H166" t="n">
-        <v>2.998280358471991</v>
+        <v>43.60069221082979</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[41105.9, 38375.57, 42219.25]</t>
+          <t>[1077.05, 1017.9, 1248.49]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[41455.0, 45002.3, 49356.3]</t>
+          <t>[1621.8, 1907.1, 2712.3]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>5626.511662550081</v>
+        <v>1037.651142849916</v>
       </c>
       <c r="G167" t="n">
-        <v>4704.292733829066</v>
+        <v>965.9194502528075</v>
       </c>
       <c r="H167" t="n">
-        <v>10.00922959933497</v>
+        <v>44.72810411300215</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[38699.13, 42570.48, 52545.23]</t>
+          <t>[1181.3, 1441.43, 1068.49]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[45002.3, 49356.3, 49099.2]</t>
+          <t>[1907.1, 2712.3, 2117.5]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>5705.330758218452</v>
+        <v>1039.602554786356</v>
       </c>
       <c r="G168" t="n">
-        <v>5511.67222348637</v>
+        <v>1015.226674850161</v>
       </c>
       <c r="H168" t="n">
-        <v>11.59115566576003</v>
+        <v>44.81786159884293</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[49442.04, 60949.86, 67999.96]</t>
+          <t>[2275.13, 1648.99, 1820.96]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[49356.3, 49099.2, 51500.3]</t>
+          <t>[2712.3, 2117.5, 2241.9]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>11728.658666231</v>
+        <v>442.6479481796361</v>
       </c>
       <c r="G169" t="n">
-        <v>9478.686470082112</v>
+        <v>442.2073737908655</v>
       </c>
       <c r="H169" t="n">
-        <v>18.78262018968382</v>
+        <v>19.00659860011151</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[60844.04, 67881.25, 80795.12]</t>
+          <t>[1953.04, 2142.71, 3414.99]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[49099.2, 51500.3, 56233.7]</t>
+          <t>[2117.5, 2241.9, 4710.8]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>18344.29911361033</v>
+        <v>756.3089633951843</v>
       </c>
       <c r="G170" t="n">
-        <v>17562.40130571234</v>
+        <v>519.8185836051547</v>
       </c>
       <c r="H170" t="n">
-        <v>33.1351701581282</v>
+        <v>13.23269566244917</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[54879.51, 65439.65, 72656.14]</t>
+          <t>[2315.9, 3679.56, 2634.88]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[51500.3, 56233.7, 58261.1]</t>
+          <t>[2241.9, 4710.8, 2247.1]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>10056.27133148432</v>
+        <v>637.5204671485186</v>
       </c>
       <c r="G171" t="n">
-        <v>8993.40049750166</v>
+        <v>497.6712818448298</v>
       </c>
       <c r="H171" t="n">
-        <v>15.88007378864214</v>
+        <v>14.14948403366866</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[61444.88, 68260.43, 57976.16]</t>
+          <t>[18430.67, 18766.49, 16041.67]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[56233.7, 58261.1, 53762.5]</t>
+          <t>[18689.8, 18071.9, 16535.5]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6949.772549178784</v>
+        <v>514.2848947570593</v>
       </c>
       <c r="G172" t="n">
-        <v>6474.724524842129</v>
+        <v>482.515991877189</v>
       </c>
       <c r="H172" t="n">
-        <v>11.42250573870388</v>
+        <v>2.738810167041788</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[62521.12, 53142.9, 44988.84]</t>
+          <t>[19028.16, 16263.23, 15187.91]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[58261.1, 53762.5, 51783.9]</t>
+          <t>[18071.9, 16535.5, 15899.2]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4644.156382363893</v>
+        <v>705.8115482918855</v>
       </c>
       <c r="G173" t="n">
-        <v>3891.563258062769</v>
+        <v>646.6091091319771</v>
       </c>
       <c r="H173" t="n">
-        <v>7.19546479488602</v>
+        <v>3.803929659893588</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[49549.59, 41975.28, 32692.64]</t>
+          <t>[16145.85, 14971.02, 14953.65]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[53762.5, 51783.9, 47959.4]</t>
+          <t>[16535.5, 15899.2, 14834.9]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>10755.3343387553</v>
+        <v>585.2187383693424</v>
       </c>
       <c r="G174" t="n">
-        <v>9762.763082216805</v>
+        <v>478.8606781337191</v>
       </c>
       <c r="H174" t="n">
-        <v>19.53675702293206</v>
+        <v>2.998280358471991</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[45512.68, 35422.59, 35041.17]</t>
+          <t>[15282.92, 15309.56, 14290.02]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[51783.9, 47959.4, 47352.0]</t>
+          <t>[15899.2, 14834.9, 15255.1]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>10771.20517113365</v>
+        <v>715.6561059917528</v>
       </c>
       <c r="G175" t="n">
-        <v>10372.95736471876</v>
+        <v>685.3413470302785</v>
       </c>
       <c r="H175" t="n">
-        <v>21.41646614474516</v>
+        <v>4.467363304078907</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[40257.21, 39779.15, 40245.62]</t>
+          <t>[15835.32, 14780.07, 13707.72]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[47959.4, 47352.0, 48441.5]</t>
+          <t>[14834.9, 15255.1, 13505.1]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>7828.242318788194</v>
+        <v>650.0101816767801</v>
       </c>
       <c r="G176" t="n">
-        <v>7823.637827344341</v>
+        <v>559.3537452977192</v>
       </c>
       <c r="H176" t="n">
-        <v>16.32386691517536</v>
+        <v>3.785954315144264</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[16951.35, 17624.95, 23584.83]</t>
+          <t>[13984.63, 13438.81, 15055.42]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[16642.4, 12543.1, 21360.2]</t>
+          <t>[15255.1, 13505.1, 14773.7]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>3207.784720385238</v>
+        <v>752.298472406055</v>
       </c>
       <c r="G177" t="n">
-        <v>2538.478130278497</v>
+        <v>539.4924002827902</v>
       </c>
       <c r="H177" t="n">
-        <v>17.59545876697252</v>
+        <v>3.575299553563658</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[17308.11, 23168.06, 24481.12]</t>
+          <t>[14470.85, 16199.27, 17545.13]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[12543.1, 21360.2, 24469.7]</t>
+          <t>[13505.1, 14773.7, 16632.7]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2942.436211902097</v>
+        <v>1125.0871858339</v>
       </c>
       <c r="G178" t="n">
-        <v>2194.763435678062</v>
+        <v>1101.251781629389</v>
       </c>
       <c r="H178" t="n">
-        <v>15.49981517262781</v>
+        <v>7.428726135077506</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[16874.69, 17921.24, 19111.43]</t>
+          <t>[15164.79, 16080.08, 17232.8]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[21360.2, 24469.7, 23754.2]</t>
+          <t>[14773.7, 16632.7, 16201.0]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>5309.031208976141</v>
+        <v>712.4937864455533</v>
       </c>
       <c r="G179" t="n">
-        <v>5225.580182325631</v>
+        <v>658.5010327846134</v>
       </c>
       <c r="H179" t="n">
-        <v>22.43531356246824</v>
+        <v>4.112798698680953</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[21795.8, 23171.39, 21622.29]</t>
+          <t>[15729.45, 16844.42, 18169.63]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[24469.7, 23754.2, 22349.7]</t>
+          <t>[16632.7, 16201.0, 16699.6]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1634.885902607271</v>
+        <v>1063.149284810912</v>
       </c>
       <c r="G180" t="n">
-        <v>1328.040880358796</v>
+        <v>1005.570037781548</v>
       </c>
       <c r="H180" t="n">
-        <v>5.545193089023645</v>
+        <v>6.068299247702826</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[25964.38, 24201.29, 22584.82]</t>
+          <t>[17667.76, 19047.55, 19760.46]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[23754.2, 22349.7, 22437.4]</t>
+          <t>[16201.0, 16699.6, 18734.2]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1666.834742269659</v>
+        <v>1704.64704782081</v>
       </c>
       <c r="G181" t="n">
-        <v>1403.062821220157</v>
+        <v>1613.65673765954</v>
       </c>
       <c r="H181" t="n">
-        <v>6.082008881900887</v>
+        <v>9.530479674687291</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[22454.31, 20977.66, 21074.61]</t>
+          <t>[49549.59, 41975.28, 32692.64]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[22349.7, 22437.4, 23808.0]</t>
+          <t>[53762.5, 51783.9, 47959.4]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1790.081762572435</v>
+        <v>10755.3343387553</v>
       </c>
       <c r="G182" t="n">
-        <v>1432.576650529752</v>
+        <v>9762.763082216805</v>
       </c>
       <c r="H182" t="n">
-        <v>6.151607553431742</v>
+        <v>19.53675702293206</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[20880.32, 20977.83, 19135.77]</t>
+          <t>[45512.68, 35422.59, 35041.17]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[22437.4, 23808.0, 22847.1]</t>
+          <t>[51783.9, 47959.4, 47352.0]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2840.678096724232</v>
+        <v>10771.20517113365</v>
       </c>
       <c r="G183" t="n">
-        <v>2699.528560694065</v>
+        <v>10372.95736471876</v>
       </c>
       <c r="H183" t="n">
-        <v>11.69045657808932</v>
+        <v>21.41646614474516</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[22522.89, 20527.18, 19713.57]</t>
+          <t>[40257.21, 39779.15, 40245.62]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[23808.0, 22847.1, 21639.9]</t>
+          <t>[47959.4, 47352.0, 48441.5]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1892.466707416615</v>
+        <v>7828.242318788194</v>
       </c>
       <c r="G184" t="n">
-        <v>1843.787190225306</v>
+        <v>7823.637827344341</v>
       </c>
       <c r="H184" t="n">
-        <v>8.151225286805149</v>
+        <v>16.32386691517536</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[21683.66, 20809.39, 18639.91]</t>
+          <t>[47315.08, 47793.61, 45863.74]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[22847.1, 21639.9, 19659.4]</t>
+          <t>[47352.0, 48441.5, 47327.0]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1013.690943855393</v>
+        <v>924.1679716289296</v>
       </c>
       <c r="G185" t="n">
-        <v>1004.481692394237</v>
+        <v>716.0220995823765</v>
       </c>
       <c r="H185" t="n">
-        <v>4.705313756417877</v>
+        <v>1.502412874447088</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[47830.07, 45898.2, 43461.14]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[48441.5, 47327.0, 44265.4]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1010.304915903269</v>
+      </c>
+      <c r="G186" t="n">
+        <v>948.163003113989</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2.032700150488889</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[46479.64, 44007.1, 48349.01]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[47327.0, 44265.4, 49073.0]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>660.5336200561693</v>
+      </c>
+      <c r="G187" t="n">
+        <v>609.8864783641014</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1.283104933223252</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[44802.41, 49215.83, 59384.3]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[44265.4, 49073.0, 52808.8]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>3809.900846116323</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2418.445830835587</v>
+      </c>
+      <c r="H188" t="n">
+        <v>4.651910816293331</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[48632.1, 58688.97, 65074.36]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[49073.0, 52808.8, 57261.1]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>5651.486277276043</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4711.445734487444</v>
+      </c>
+      <c r="H189" t="n">
+        <v>8.559423609358374</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[59213.04, 65658.73, 77482.45]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[52808.8, 57261.1, 59281.5]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>12149.19997645825</v>
+      </c>
+      <c r="G190" t="n">
+        <v>11000.94141835216</v>
+      </c>
+      <c r="H190" t="n">
+        <v>19.16510490880941</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[58606.99, 69224.74, 76274.94]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[57261.1, 59281.5, 63008.6]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>9603.385197420925</v>
+      </c>
+      <c r="G191" t="n">
+        <v>8185.155133875021</v>
+      </c>
+      <c r="H191" t="n">
+        <v>13.39272253659351</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[22522.89, 20527.18, 19713.57]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[23808.0, 22847.1, 21639.9]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1892.466707416615</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1843.787190225306</v>
+      </c>
+      <c r="H192" t="n">
+        <v>8.151225286805149</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[21683.66, 20809.39, 18639.91]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[22847.1, 21639.9, 19659.4]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1013.690943855393</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1004.481692394237</v>
+      </c>
+      <c r="H193" t="n">
+        <v>4.705313756417877</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[21783.93, 19502.85, 20406.05]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[21639.9, 19659.4, 19576.8]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>494.2710816140799</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>376.6112260107329</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>1.899262606702426</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[19374.25, 20274.74, 18105.75]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[19659.4, 19576.8, 18830.5]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>603.7938766827621</v>
+      </c>
+      <c r="G195" t="n">
+        <v>569.2823727897157</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2.954811835024601</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[20568.14, 18364.47, 18081.92]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[19576.8, 18830.5, 16545.6]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1089.377232370136</v>
+      </c>
+      <c r="G196" t="n">
+        <v>997.89912434772</v>
+      </c>
+      <c r="H196" t="n">
+        <v>5.608042255980458</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[17490.44, 17231.92, 23998.96]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[18830.5, 16545.6, 21272.4]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1798.231520716225</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1584.312835032274</v>
+      </c>
+      <c r="H197" t="n">
+        <v>8.027280368447407</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[18534.04, 25788.23, 27580.57]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[16545.6, 21272.4, 23757.1]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>3603.956473544382</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3442.578042835322</v>
+      </c>
+      <c r="H198" t="n">
+        <v>16.44683411153496</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[23512.96, 25178.19, 26315.98]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[21272.4, 23757.1, 25319.1]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1636.395059827736</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1552.842540810621</v>
+      </c>
+      <c r="H199" t="n">
+        <v>6.817237225828032</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[23065.8, 24137.61, 22551.23]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[23757.1, 25319.1, 27352.3]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>2882.365303585152</v>
+      </c>
+      <c r="G200" t="n">
+        <v>2224.619682794952</v>
+      </c>
+      <c r="H200" t="n">
+        <v>8.376323717943889</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[24850.96, 23212.33, 21899.67]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[25319.1, 27352.3, 23460.7]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>2568.742443786353</v>
+      </c>
+      <c r="G201" t="n">
+        <v>2056.380660037098</v>
+      </c>
+      <c r="H201" t="n">
+        <v>7.879502040319021</v>
       </c>
     </row>
   </sheetData>
